--- a/research/traditional_assets/database/data/france/france_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/france/france_shipbuilding_marine.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08989338340509831</v>
+        <v>0.08970239994658556</v>
       </c>
       <c r="C2">
-        <v>376.9044355781197</v>
+        <v>373.3294423852292</v>
       </c>
       <c r="D2">
-        <v>335.5044355781197</v>
+        <v>335.9592515953242</v>
       </c>
       <c r="E2">
-        <v>-376.2809210094953</v>
+        <v>-372.2511117994004</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.029809210094953</v>
       </c>
       <c r="G2">
         <v>41.4</v>
@@ -1445,28 +1445,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2026994032677761</v>
       </c>
       <c r="N2">
-        <v>64.25333333333333</v>
+        <v>64.05063393006556</v>
       </c>
       <c r="O2">
-        <v>16.06333333333333</v>
+        <v>16.01265848251639</v>
       </c>
       <c r="P2">
-        <v>48.19</v>
+        <v>48.03797544754917</v>
       </c>
       <c r="Q2">
-        <v>81.59</v>
+        <v>81.43797544754918</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08989338340509831</v>
+        <v>0.09022742418847027</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367391</v>
+        <v>0.8659731901544416</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>316.9882707964929</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08970239994658556</v>
+        <v>0.08951141648807283</v>
       </c>
       <c r="C3">
-        <v>373.3294423852292</v>
+        <v>369.7556839802473</v>
       </c>
       <c r="D3">
-        <v>335.9592515953242</v>
+        <v>336.4153024004372</v>
       </c>
       <c r="E3">
-        <v>-372.2511117994004</v>
+        <v>-368.2213025893054</v>
       </c>
       <c r="F3">
-        <v>4.029809210094953</v>
+        <v>8.059618420189906</v>
       </c>
       <c r="G3">
         <v>41.4</v>
@@ -1527,28 +1527,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M3">
-        <v>0.2026994032677761</v>
+        <v>0.4053988065355523</v>
       </c>
       <c r="N3">
-        <v>64.05063393006556</v>
+        <v>63.84793452679778</v>
       </c>
       <c r="O3">
-        <v>16.01265848251639</v>
+        <v>15.96198363169944</v>
       </c>
       <c r="P3">
-        <v>48.03797544754917</v>
+        <v>47.88595089509833</v>
       </c>
       <c r="Q3">
-        <v>81.43797544754918</v>
+        <v>81.28595089509832</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09022742418847027</v>
+        <v>0.09056828213068656</v>
       </c>
       <c r="T3">
-        <v>0.8659731901544416</v>
+        <v>0.8726171458867913</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>316.9882707964929</v>
+        <v>158.4941353982464</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08951141648807283</v>
+        <v>0.08932043302956007</v>
       </c>
       <c r="C4">
-        <v>369.7556839802473</v>
+        <v>366.18316539853</v>
       </c>
       <c r="D4">
-        <v>336.4153024004372</v>
+        <v>336.8725930288149</v>
       </c>
       <c r="E4">
-        <v>-368.2213025893054</v>
+        <v>-364.1914933792104</v>
       </c>
       <c r="F4">
-        <v>8.059618420189906</v>
+        <v>12.08942763028486</v>
       </c>
       <c r="G4">
         <v>41.4</v>
@@ -1609,28 +1609,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M4">
-        <v>0.4053988065355523</v>
+        <v>0.6080982098033284</v>
       </c>
       <c r="N4">
-        <v>63.84793452679778</v>
+        <v>63.64523512353</v>
       </c>
       <c r="O4">
-        <v>15.96198363169944</v>
+        <v>15.9113087808825</v>
       </c>
       <c r="P4">
-        <v>47.88595089509833</v>
+        <v>47.7339263426475</v>
       </c>
       <c r="Q4">
-        <v>81.28595089509832</v>
+        <v>81.1339263426475</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09056828213068656</v>
+        <v>0.09091616807171141</v>
       </c>
       <c r="T4">
-        <v>0.8726171458867913</v>
+        <v>0.8793980903971272</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>158.4941353982464</v>
+        <v>105.6627569321643</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08932043302956007</v>
+        <v>0.08912944957104732</v>
       </c>
       <c r="C5">
-        <v>366.18316539853</v>
+        <v>362.611891702849</v>
       </c>
       <c r="D5">
-        <v>336.8725930288149</v>
+        <v>337.3311285432288</v>
       </c>
       <c r="E5">
-        <v>-364.1914933792104</v>
+        <v>-360.1616841691155</v>
       </c>
       <c r="F5">
-        <v>12.08942763028486</v>
+        <v>16.11923684037981</v>
       </c>
       <c r="G5">
         <v>41.4</v>
@@ -1691,28 +1691,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M5">
-        <v>0.6080982098033284</v>
+        <v>0.8107976130711045</v>
       </c>
       <c r="N5">
-        <v>63.64523512353</v>
+        <v>63.44253572026223</v>
       </c>
       <c r="O5">
-        <v>15.9113087808825</v>
+        <v>15.86063393006556</v>
       </c>
       <c r="P5">
-        <v>47.7339263426475</v>
+        <v>47.58190179019667</v>
       </c>
       <c r="Q5">
-        <v>81.1339263426475</v>
+        <v>80.98190179019667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09091616807171141</v>
+        <v>0.09127130163650764</v>
       </c>
       <c r="T5">
-        <v>0.8793980903971272</v>
+        <v>0.8863203045847622</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>105.6627569321643</v>
+        <v>79.24706769912322</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08912944957104732</v>
+        <v>0.08893846611253457</v>
       </c>
       <c r="C6">
-        <v>362.611891702849</v>
+        <v>359.0418679835782</v>
       </c>
       <c r="D6">
-        <v>337.3311285432288</v>
+        <v>337.7909140340529</v>
       </c>
       <c r="E6">
-        <v>-360.1616841691155</v>
+        <v>-356.1318749590206</v>
       </c>
       <c r="F6">
-        <v>16.11923684037981</v>
+        <v>20.14904605047477</v>
       </c>
       <c r="G6">
         <v>41.4</v>
@@ -1773,28 +1773,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M6">
-        <v>0.8107976130711045</v>
+        <v>1.013497016338881</v>
       </c>
       <c r="N6">
-        <v>63.44253572026223</v>
+        <v>63.23983631699445</v>
       </c>
       <c r="O6">
-        <v>15.86063393006556</v>
+        <v>15.80995907924861</v>
       </c>
       <c r="P6">
-        <v>47.58190179019667</v>
+        <v>47.42987723774583</v>
       </c>
       <c r="Q6">
-        <v>80.98190179019667</v>
+        <v>80.82987723774583</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09127130163650764</v>
+        <v>0.09163391169740481</v>
       </c>
       <c r="T6">
-        <v>0.8863203045847622</v>
+        <v>0.8933882495973998</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>79.24706769912322</v>
+        <v>63.39765415929856</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08893846611253457</v>
+        <v>0.08874748265402184</v>
       </c>
       <c r="C7">
-        <v>359.0418679835782</v>
+        <v>355.4730993588823</v>
       </c>
       <c r="D7">
-        <v>337.7909140340529</v>
+        <v>338.2519546194521</v>
       </c>
       <c r="E7">
-        <v>-356.1318749590206</v>
+        <v>-352.1020657489256</v>
       </c>
       <c r="F7">
-        <v>20.14904605047477</v>
+        <v>24.17885526056972</v>
       </c>
       <c r="G7">
         <v>41.4</v>
@@ -1855,28 +1855,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M7">
-        <v>1.013497016338881</v>
+        <v>1.216196419606657</v>
       </c>
       <c r="N7">
-        <v>63.23983631699445</v>
+        <v>63.03713691372667</v>
       </c>
       <c r="O7">
-        <v>15.80995907924861</v>
+        <v>15.75928422843167</v>
       </c>
       <c r="P7">
-        <v>47.42987723774583</v>
+        <v>47.277852685295</v>
       </c>
       <c r="Q7">
-        <v>80.82987723774583</v>
+        <v>80.67785268529499</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09163391169740481</v>
+        <v>0.09200423686598068</v>
       </c>
       <c r="T7">
-        <v>0.8933882495973998</v>
+        <v>0.900606576418817</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>63.39765415929856</v>
+        <v>52.83137846608213</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08874748265402184</v>
+        <v>0.08855649919550908</v>
       </c>
       <c r="C8">
-        <v>355.4730993588823</v>
+        <v>351.9055909749071</v>
       </c>
       <c r="D8">
-        <v>338.2519546194521</v>
+        <v>338.7142554455717</v>
       </c>
       <c r="E8">
-        <v>-352.1020657489256</v>
+        <v>-348.0722565388307</v>
       </c>
       <c r="F8">
-        <v>24.17885526056972</v>
+        <v>28.20866447066467</v>
       </c>
       <c r="G8">
         <v>41.4</v>
@@ -1937,28 +1937,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M8">
-        <v>1.216196419606657</v>
+        <v>1.418895822874433</v>
       </c>
       <c r="N8">
-        <v>63.03713691372668</v>
+        <v>62.8344375104589</v>
       </c>
       <c r="O8">
-        <v>15.75928422843167</v>
+        <v>15.70860937761472</v>
       </c>
       <c r="P8">
-        <v>47.27785268529501</v>
+        <v>47.12582813284418</v>
       </c>
       <c r="Q8">
-        <v>80.67785268529501</v>
+        <v>80.52582813284417</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09200423686598068</v>
+        <v>0.09238252601667643</v>
       </c>
       <c r="T8">
-        <v>0.900606576418817</v>
+        <v>0.9079801360751033</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>52.83137846608214</v>
+        <v>45.28403868521327</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08855649919550908</v>
+        <v>0.08836551573699636</v>
       </c>
       <c r="C9">
-        <v>351.905590974907</v>
+        <v>348.3393480059698</v>
       </c>
       <c r="D9">
-        <v>338.7142554455717</v>
+        <v>339.1778216867295</v>
       </c>
       <c r="E9">
-        <v>-348.0722565388306</v>
+        <v>-344.0424473287357</v>
       </c>
       <c r="F9">
-        <v>28.20866447066468</v>
+        <v>32.23847368075963</v>
       </c>
       <c r="G9">
         <v>41.4</v>
@@ -2019,28 +2019,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M9">
-        <v>1.418895822874433</v>
+        <v>1.621595226142209</v>
       </c>
       <c r="N9">
-        <v>62.8344375104589</v>
+        <v>62.63173810719112</v>
       </c>
       <c r="O9">
-        <v>15.70860937761472</v>
+        <v>15.65793452679778</v>
       </c>
       <c r="P9">
-        <v>47.12582813284418</v>
+        <v>46.97380358039334</v>
       </c>
       <c r="Q9">
-        <v>80.52582813284417</v>
+        <v>80.37380358039334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09238252601667643</v>
+        <v>0.09276903884456125</v>
       </c>
       <c r="T9">
-        <v>0.9079801360751033</v>
+        <v>0.9155139905065265</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.28403868521326</v>
+        <v>39.6235338495616</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08836551573699636</v>
+        <v>0.0881745322784836</v>
       </c>
       <c r="C10">
-        <v>348.3393480059698</v>
+        <v>344.774375654754</v>
       </c>
       <c r="D10">
-        <v>339.1778216867295</v>
+        <v>339.6426585456085</v>
       </c>
       <c r="E10">
-        <v>-344.0424473287357</v>
+        <v>-340.0126381186408</v>
       </c>
       <c r="F10">
-        <v>32.23847368075963</v>
+        <v>36.26828289085458</v>
       </c>
       <c r="G10">
         <v>41.4</v>
@@ -2101,28 +2101,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M10">
-        <v>1.621595226142209</v>
+        <v>1.824294629409985</v>
       </c>
       <c r="N10">
-        <v>62.63173810719112</v>
+        <v>62.42903870392335</v>
       </c>
       <c r="O10">
-        <v>15.65793452679778</v>
+        <v>15.60725967598084</v>
       </c>
       <c r="P10">
-        <v>46.97380358039334</v>
+        <v>46.82177902794251</v>
       </c>
       <c r="Q10">
-        <v>80.37380358039334</v>
+        <v>80.22177902794252</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09276903884456125</v>
+        <v>0.09316404645987209</v>
       </c>
       <c r="T10">
-        <v>0.9155139905065265</v>
+        <v>0.9232134241562224</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>39.6235338495616</v>
+        <v>35.2209189773881</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0881745322784836</v>
+        <v>0.08798354881997084</v>
       </c>
       <c r="C11">
-        <v>344.774375654754</v>
+        <v>341.2106791525019</v>
       </c>
       <c r="D11">
-        <v>339.6426585456085</v>
+        <v>340.1087712534514</v>
       </c>
       <c r="E11">
-        <v>-340.0126381186408</v>
+        <v>-335.9828289085458</v>
       </c>
       <c r="F11">
-        <v>36.26828289085458</v>
+        <v>40.29809210094953</v>
       </c>
       <c r="G11">
         <v>41.4</v>
@@ -2183,28 +2183,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M11">
-        <v>1.824294629409985</v>
+        <v>2.026994032677762</v>
       </c>
       <c r="N11">
-        <v>62.42903870392335</v>
+        <v>62.22633930065557</v>
       </c>
       <c r="O11">
-        <v>15.60725967598084</v>
+        <v>15.55658482516389</v>
       </c>
       <c r="P11">
-        <v>46.82177902794251</v>
+        <v>46.66975447549167</v>
       </c>
       <c r="Q11">
-        <v>80.22177902794252</v>
+        <v>80.06975447549166</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09316404645987209</v>
+        <v>0.09356783202218982</v>
       </c>
       <c r="T11">
-        <v>0.9232134241562224</v>
+        <v>0.9310839563314672</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.2209189773881</v>
+        <v>31.69882707964928</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08798354881997084</v>
+        <v>0.08779256536145812</v>
       </c>
       <c r="C12">
-        <v>341.2106791525019</v>
+        <v>337.6482637592125</v>
       </c>
       <c r="D12">
-        <v>340.1087712534514</v>
+        <v>340.5761650702569</v>
       </c>
       <c r="E12">
-        <v>-335.9828289085458</v>
+        <v>-331.9530196984508</v>
       </c>
       <c r="F12">
-        <v>40.29809210094953</v>
+        <v>44.32790131104449</v>
       </c>
       <c r="G12">
         <v>41.4</v>
@@ -2265,28 +2265,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M12">
-        <v>2.026994032677762</v>
+        <v>2.229693435945538</v>
       </c>
       <c r="N12">
-        <v>62.22633930065557</v>
+        <v>62.0236398973878</v>
       </c>
       <c r="O12">
-        <v>15.55658482516389</v>
+        <v>15.50590997434695</v>
       </c>
       <c r="P12">
-        <v>46.66975447549167</v>
+        <v>46.51772992304085</v>
       </c>
       <c r="Q12">
-        <v>80.06975447549166</v>
+        <v>79.91772992304084</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09356783202218982</v>
+        <v>0.09398069141736867</v>
       </c>
       <c r="T12">
-        <v>0.9310839563314672</v>
+        <v>0.9391313543982908</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.69882707964928</v>
+        <v>28.81711552695389</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08779256536145812</v>
+        <v>0.08760158190294537</v>
       </c>
       <c r="C13">
-        <v>337.6482637592125</v>
+        <v>334.0871347638387</v>
       </c>
       <c r="D13">
-        <v>340.5761650702569</v>
+        <v>341.0448452849781</v>
       </c>
       <c r="E13">
-        <v>-331.9530196984508</v>
+        <v>-327.9232104883559</v>
       </c>
       <c r="F13">
-        <v>44.32790131104449</v>
+        <v>48.35771052113944</v>
       </c>
       <c r="G13">
         <v>41.4</v>
@@ -2347,28 +2347,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M13">
-        <v>2.229693435945538</v>
+        <v>2.432392839213314</v>
       </c>
       <c r="N13">
-        <v>62.0236398973878</v>
+        <v>61.82094049412002</v>
       </c>
       <c r="O13">
-        <v>15.50590997434695</v>
+        <v>15.45523512353</v>
       </c>
       <c r="P13">
-        <v>46.51772992304085</v>
+        <v>46.36570537059001</v>
       </c>
       <c r="Q13">
-        <v>79.91772992304084</v>
+        <v>79.76570537059001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09398069141736867</v>
+        <v>0.09440293398061973</v>
       </c>
       <c r="T13">
-        <v>0.9391313543982908</v>
+        <v>0.9473616478757237</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.81711552695389</v>
+        <v>26.41568923304107</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08760158190294537</v>
+        <v>0.08741059844443261</v>
       </c>
       <c r="C14">
-        <v>334.0871347638387</v>
+        <v>330.5272974844868</v>
       </c>
       <c r="D14">
-        <v>341.0448452849781</v>
+        <v>341.5148172157212</v>
       </c>
       <c r="E14">
-        <v>-327.9232104883559</v>
+        <v>-323.893401278261</v>
       </c>
       <c r="F14">
-        <v>48.35771052113944</v>
+        <v>52.38751973123439</v>
       </c>
       <c r="G14">
         <v>41.4</v>
@@ -2429,28 +2429,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M14">
-        <v>2.432392839213314</v>
+        <v>2.63509224248109</v>
       </c>
       <c r="N14">
-        <v>61.82094049412002</v>
+        <v>61.61824109085224</v>
       </c>
       <c r="O14">
-        <v>15.45523512353</v>
+        <v>15.40456027271306</v>
       </c>
       <c r="P14">
-        <v>46.36570537059001</v>
+        <v>46.21368081813918</v>
       </c>
       <c r="Q14">
-        <v>79.76570537059001</v>
+        <v>79.61368081813919</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09440293398061973</v>
+        <v>0.09483488326946277</v>
       </c>
       <c r="T14">
-        <v>0.9473616478757237</v>
+        <v>0.9557811435020632</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.41568923304107</v>
+        <v>24.38371313819176</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08741059844443261</v>
+        <v>0.08721961498591986</v>
       </c>
       <c r="C15">
-        <v>330.5272974844868</v>
+        <v>326.9687572686176</v>
       </c>
       <c r="D15">
-        <v>341.5148172157212</v>
+        <v>341.986086209947</v>
       </c>
       <c r="E15">
-        <v>-323.893401278261</v>
+        <v>-319.863592068166</v>
       </c>
       <c r="F15">
-        <v>52.38751973123439</v>
+        <v>56.41732894132935</v>
       </c>
       <c r="G15">
         <v>41.4</v>
@@ -2511,28 +2511,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M15">
-        <v>2.63509224248109</v>
+        <v>2.837791645748866</v>
       </c>
       <c r="N15">
-        <v>61.61824109085224</v>
+        <v>61.41554168758447</v>
       </c>
       <c r="O15">
-        <v>15.40456027271306</v>
+        <v>15.35388542189612</v>
       </c>
       <c r="P15">
-        <v>46.21368081813918</v>
+        <v>46.06165626568835</v>
       </c>
       <c r="Q15">
-        <v>79.61368081813919</v>
+        <v>79.46165626568835</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09483488326946277</v>
+        <v>0.0952768778906045</v>
       </c>
       <c r="T15">
-        <v>0.9557811435020632</v>
+        <v>0.9643964413522712</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.38371313819176</v>
+        <v>22.64201934260663</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08721961498591986</v>
+        <v>0.08702863152740713</v>
       </c>
       <c r="C16">
-        <v>326.9687572686176</v>
+        <v>323.4115194932494</v>
       </c>
       <c r="D16">
-        <v>341.986086209947</v>
+        <v>342.4586576446738</v>
       </c>
       <c r="E16">
-        <v>-319.863592068166</v>
+        <v>-315.833782858071</v>
       </c>
       <c r="F16">
-        <v>56.41732894132935</v>
+        <v>60.4471381514243</v>
       </c>
       <c r="G16">
         <v>41.4</v>
@@ -2593,28 +2593,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M16">
-        <v>2.837791645748866</v>
+        <v>3.040491049016643</v>
       </c>
       <c r="N16">
-        <v>61.41554168758447</v>
+        <v>61.21284228431669</v>
       </c>
       <c r="O16">
-        <v>15.35388542189612</v>
+        <v>15.30321057107917</v>
       </c>
       <c r="P16">
-        <v>46.06165626568835</v>
+        <v>45.90963171323752</v>
       </c>
       <c r="Q16">
-        <v>79.46165626568835</v>
+        <v>79.30963171323751</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0952768778906045</v>
+        <v>0.09572927238518485</v>
       </c>
       <c r="T16">
-        <v>0.9643964413522712</v>
+        <v>0.9732144520930721</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.64201934260663</v>
+        <v>21.13255138643285</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08702863152740713</v>
+        <v>0.08683764806889437</v>
       </c>
       <c r="C17">
-        <v>323.4115194932494</v>
+        <v>319.8555895651627</v>
       </c>
       <c r="D17">
-        <v>342.4586576446738</v>
+        <v>342.932536926682</v>
       </c>
       <c r="E17">
-        <v>-315.833782858071</v>
+        <v>-311.8039736479761</v>
       </c>
       <c r="F17">
-        <v>60.4471381514243</v>
+        <v>64.47694736151925</v>
       </c>
       <c r="G17">
         <v>41.4</v>
@@ -2675,28 +2675,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M17">
-        <v>3.040491049016642</v>
+        <v>3.243190452284418</v>
       </c>
       <c r="N17">
-        <v>61.21284228431669</v>
+        <v>61.01014288104891</v>
       </c>
       <c r="O17">
-        <v>15.30321057107917</v>
+        <v>15.25253572026223</v>
       </c>
       <c r="P17">
-        <v>45.90963171323752</v>
+        <v>45.75760716078668</v>
       </c>
       <c r="Q17">
-        <v>79.30963171323751</v>
+        <v>79.15760716078668</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09572927238518485</v>
+        <v>0.0961924381772552</v>
       </c>
       <c r="T17">
-        <v>0.9732144520930721</v>
+        <v>0.9822424154705589</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.13255138643285</v>
+        <v>19.81176692478081</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08683764806889437</v>
+        <v>0.08664666461038163</v>
       </c>
       <c r="C18">
-        <v>319.8555895651627</v>
+        <v>316.3009729211058</v>
       </c>
       <c r="D18">
-        <v>342.932536926682</v>
+        <v>343.40772949272</v>
       </c>
       <c r="E18">
-        <v>-311.8039736479761</v>
+        <v>-307.7741644378812</v>
       </c>
       <c r="F18">
-        <v>64.47694736151925</v>
+        <v>68.5067565716142</v>
       </c>
       <c r="G18">
         <v>41.4</v>
@@ -2757,28 +2757,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M18">
-        <v>3.243190452284418</v>
+        <v>3.445889855552194</v>
       </c>
       <c r="N18">
-        <v>61.01014288104891</v>
+        <v>60.80744347778113</v>
       </c>
       <c r="O18">
-        <v>15.25253572026223</v>
+        <v>15.20186086944528</v>
       </c>
       <c r="P18">
-        <v>45.75760716078668</v>
+        <v>45.60558260833585</v>
       </c>
       <c r="Q18">
-        <v>79.15760716078668</v>
+        <v>79.00558260833586</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0961924381772552</v>
+        <v>0.09666676459082126</v>
       </c>
       <c r="T18">
-        <v>0.9822424154705589</v>
+        <v>0.9914879201342504</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.81176692478081</v>
+        <v>18.64636887038193</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08664666461038163</v>
+        <v>0.08645568115186887</v>
       </c>
       <c r="C19">
-        <v>316.3009729211058</v>
+        <v>312.7476750280029</v>
       </c>
       <c r="D19">
-        <v>343.40772949272</v>
+        <v>343.8842408097121</v>
       </c>
       <c r="E19">
-        <v>-307.7741644378812</v>
+        <v>-303.7443552277862</v>
       </c>
       <c r="F19">
-        <v>68.5067565716142</v>
+        <v>72.53656578170917</v>
       </c>
       <c r="G19">
         <v>41.4</v>
@@ -2839,28 +2839,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M19">
-        <v>3.445889855552194</v>
+        <v>3.648589258819971</v>
       </c>
       <c r="N19">
-        <v>60.80744347778113</v>
+        <v>60.60474407451336</v>
       </c>
       <c r="O19">
-        <v>15.20186086944528</v>
+        <v>15.15118601862834</v>
       </c>
       <c r="P19">
-        <v>45.60558260833585</v>
+        <v>45.45355805588503</v>
       </c>
       <c r="Q19">
-        <v>79.00558260833586</v>
+        <v>78.85355805588503</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09666676459082126</v>
+        <v>0.09715265994130351</v>
       </c>
       <c r="T19">
-        <v>0.9914879201342504</v>
+        <v>1.00095892491169</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.64636887038193</v>
+        <v>17.61045948869404</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08645568115186889</v>
+        <v>0.08626469769335615</v>
       </c>
       <c r="C20">
-        <v>312.7476750280028</v>
+        <v>309.1957013831643</v>
       </c>
       <c r="D20">
-        <v>343.884240809712</v>
+        <v>344.3620763749684</v>
       </c>
       <c r="E20">
-        <v>-303.7443552277862</v>
+        <v>-299.7145460176912</v>
       </c>
       <c r="F20">
-        <v>72.53656578170916</v>
+        <v>76.56637499180411</v>
       </c>
       <c r="G20">
         <v>41.4</v>
@@ -2921,28 +2921,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M20">
-        <v>3.648589258819971</v>
+        <v>3.851288662087747</v>
       </c>
       <c r="N20">
-        <v>60.60474407451336</v>
+        <v>60.40204467124558</v>
       </c>
       <c r="O20">
-        <v>15.15118601862834</v>
+        <v>15.1005111678114</v>
       </c>
       <c r="P20">
-        <v>45.45355805588503</v>
+        <v>45.30153350343419</v>
       </c>
       <c r="Q20">
-        <v>78.85355805588503</v>
+        <v>78.70153350343418</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09715265994130351</v>
+        <v>0.09765055270784709</v>
       </c>
       <c r="T20">
-        <v>1.00095892491169</v>
+        <v>1.010663781658943</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.61045948869405</v>
+        <v>16.68359319981541</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08626469769335615</v>
+        <v>0.0860737142348434</v>
       </c>
       <c r="C21">
-        <v>309.1957013831643</v>
+        <v>305.6450575144973</v>
       </c>
       <c r="D21">
-        <v>344.3620763749684</v>
+        <v>344.8412417163964</v>
       </c>
       <c r="E21">
-        <v>-299.7145460176912</v>
+        <v>-295.6847368075963</v>
       </c>
       <c r="F21">
-        <v>76.56637499180411</v>
+        <v>80.59618420189906</v>
       </c>
       <c r="G21">
         <v>41.4</v>
@@ -3003,28 +3003,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M21">
-        <v>3.851288662087747</v>
+        <v>4.053988065355523</v>
       </c>
       <c r="N21">
-        <v>60.40204467124558</v>
+        <v>60.1993452679778</v>
       </c>
       <c r="O21">
-        <v>15.1005111678114</v>
+        <v>15.04983631699445</v>
       </c>
       <c r="P21">
-        <v>45.30153350343419</v>
+        <v>45.14950895098335</v>
       </c>
       <c r="Q21">
-        <v>78.70153350343418</v>
+        <v>78.54950895098335</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09765055270784709</v>
+        <v>0.09816089279355425</v>
       </c>
       <c r="T21">
-        <v>1.010663781658943</v>
+        <v>1.020611259824878</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.68359319981541</v>
+        <v>15.84941353982464</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0860737142348434</v>
+        <v>0.08588273077633066</v>
       </c>
       <c r="C22">
-        <v>305.6450575144973</v>
+        <v>302.0957489807193</v>
       </c>
       <c r="D22">
-        <v>344.8412417163964</v>
+        <v>345.3217423927134</v>
       </c>
       <c r="E22">
-        <v>-295.6847368075963</v>
+        <v>-291.6549275975013</v>
       </c>
       <c r="F22">
-        <v>80.59618420189906</v>
+        <v>84.62599341199403</v>
       </c>
       <c r="G22">
         <v>41.4</v>
@@ -3085,28 +3085,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M22">
-        <v>4.053988065355523</v>
+        <v>4.2566874686233</v>
       </c>
       <c r="N22">
-        <v>60.1993452679778</v>
+        <v>59.99664586471003</v>
       </c>
       <c r="O22">
-        <v>15.04983631699445</v>
+        <v>14.99916146617751</v>
       </c>
       <c r="P22">
-        <v>45.14950895098335</v>
+        <v>44.99748439853252</v>
       </c>
       <c r="Q22">
-        <v>78.54950895098335</v>
+        <v>78.39748439853253</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09816089279355425</v>
+        <v>0.0986841528814312</v>
       </c>
       <c r="T22">
-        <v>1.020611259824878</v>
+        <v>1.030810572881089</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.84941353982464</v>
+        <v>15.09467956173775</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08588273077633066</v>
+        <v>0.08569174731781791</v>
       </c>
       <c r="C23">
-        <v>302.0957489807193</v>
+        <v>298.5477813715731</v>
       </c>
       <c r="D23">
-        <v>345.3217423927134</v>
+        <v>345.8035839936621</v>
       </c>
       <c r="E23">
-        <v>-291.6549275975013</v>
+        <v>-287.6251183874064</v>
       </c>
       <c r="F23">
-        <v>84.62599341199402</v>
+        <v>88.65580262208897</v>
       </c>
       <c r="G23">
         <v>41.4</v>
@@ -3167,28 +3167,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M23">
-        <v>4.256687468623299</v>
+        <v>4.459386871891075</v>
       </c>
       <c r="N23">
-        <v>59.99664586471003</v>
+        <v>59.79394646144225</v>
       </c>
       <c r="O23">
-        <v>14.99916146617751</v>
+        <v>14.94848661536056</v>
       </c>
       <c r="P23">
-        <v>44.99748439853252</v>
+        <v>44.84545984608169</v>
       </c>
       <c r="Q23">
-        <v>78.39748439853253</v>
+        <v>78.24545984608169</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0986841528814312</v>
+        <v>0.09922082989463835</v>
       </c>
       <c r="T23">
-        <v>1.030810572881089</v>
+        <v>1.041271406784895</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.09467956173776</v>
+        <v>14.40855776347695</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08569174731781791</v>
+        <v>0.08550076385930515</v>
       </c>
       <c r="C24">
-        <v>298.5477813715731</v>
+        <v>295.0011603080435</v>
       </c>
       <c r="D24">
-        <v>345.8035839936621</v>
+        <v>346.2867721402274</v>
       </c>
       <c r="E24">
-        <v>-287.6251183874064</v>
+        <v>-283.5953091773114</v>
       </c>
       <c r="F24">
-        <v>88.65580262208897</v>
+        <v>92.68561183218392</v>
       </c>
       <c r="G24">
         <v>41.4</v>
@@ -3249,28 +3249,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M24">
-        <v>4.459386871891075</v>
+        <v>4.662086275158851</v>
       </c>
       <c r="N24">
-        <v>59.79394646144225</v>
+        <v>59.59124705817448</v>
       </c>
       <c r="O24">
-        <v>14.94848661536056</v>
+        <v>14.89781176454362</v>
       </c>
       <c r="P24">
-        <v>44.84545984608169</v>
+        <v>44.69343529363086</v>
       </c>
       <c r="Q24">
-        <v>78.24545984608169</v>
+        <v>78.09343529363086</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09922082989463835</v>
+        <v>0.09977144657052617</v>
       </c>
       <c r="T24">
-        <v>1.041271406784895</v>
+        <v>1.052003950660229</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.40855776347695</v>
+        <v>13.7820987302823</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08550076385930515</v>
+        <v>0.0853097804007924</v>
       </c>
       <c r="C25">
-        <v>295.0011603080435</v>
+        <v>291.4558914425756</v>
       </c>
       <c r="D25">
-        <v>346.2867721402274</v>
+        <v>346.7713124848545</v>
       </c>
       <c r="E25">
-        <v>-283.5953091773114</v>
+        <v>-279.5654999672165</v>
       </c>
       <c r="F25">
-        <v>92.68561183218392</v>
+        <v>96.71542104227889</v>
       </c>
       <c r="G25">
         <v>41.4</v>
@@ -3331,28 +3331,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M25">
-        <v>4.662086275158851</v>
+        <v>4.864785678426628</v>
       </c>
       <c r="N25">
-        <v>59.59124705817448</v>
+        <v>59.3885476549067</v>
       </c>
       <c r="O25">
-        <v>14.89781176454362</v>
+        <v>14.84713691372668</v>
       </c>
       <c r="P25">
-        <v>44.69343529363086</v>
+        <v>44.54141074118003</v>
       </c>
       <c r="Q25">
-        <v>78.09343529363086</v>
+        <v>77.94141074118002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09977144657052617</v>
+        <v>0.1003365531589374</v>
       </c>
       <c r="T25">
-        <v>1.052003950660229</v>
+        <v>1.063018929900704</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.7820987302823</v>
+        <v>13.20784461652053</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0853097804007924</v>
+        <v>0.08540004694227966</v>
       </c>
       <c r="C26">
-        <v>291.4558914425756</v>
+        <v>287.1968999018342</v>
       </c>
       <c r="D26">
-        <v>346.7713124848545</v>
+        <v>346.542130154208</v>
       </c>
       <c r="E26">
-        <v>-279.5654999672165</v>
+        <v>-275.5356907571215</v>
       </c>
       <c r="F26">
-        <v>96.71542104227888</v>
+        <v>100.7452302523738</v>
       </c>
       <c r="G26">
         <v>41.4</v>
@@ -3413,45 +3413,45 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M26">
-        <v>4.864785678426627</v>
+        <v>5.218602927072964</v>
       </c>
       <c r="N26">
-        <v>59.3885476549067</v>
+        <v>59.03473040626037</v>
       </c>
       <c r="O26">
-        <v>14.84713691372668</v>
+        <v>14.75868260156509</v>
       </c>
       <c r="P26">
-        <v>44.54141074118003</v>
+        <v>44.27604780469527</v>
       </c>
       <c r="Q26">
-        <v>77.94141074118002</v>
+        <v>77.67604780469527</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1003365531589374</v>
+        <v>0.1009167292563729</v>
       </c>
       <c r="T26">
-        <v>1.063018929900704</v>
+        <v>1.074327641920924</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.20784461652054</v>
+        <v>12.31236295062826</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08540004694227966</v>
+        <v>0.08522031348376694</v>
       </c>
       <c r="C27">
-        <v>287.1968999018342</v>
+        <v>283.6237244608714</v>
       </c>
       <c r="D27">
-        <v>346.542130154208</v>
+        <v>346.9987639233402</v>
       </c>
       <c r="E27">
-        <v>-275.5356907571215</v>
+        <v>-271.5058815470265</v>
       </c>
       <c r="F27">
-        <v>100.7452302523738</v>
+        <v>104.7750394624688</v>
       </c>
       <c r="G27">
         <v>41.4</v>
@@ -3495,28 +3495,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M27">
-        <v>5.218602927072964</v>
+        <v>5.427347044155883</v>
       </c>
       <c r="N27">
-        <v>59.03473040626037</v>
+        <v>58.82598628917745</v>
       </c>
       <c r="O27">
-        <v>14.75868260156509</v>
+        <v>14.70649657229436</v>
       </c>
       <c r="P27">
-        <v>44.27604780469527</v>
+        <v>44.11948971688309</v>
       </c>
       <c r="Q27">
-        <v>77.67604780469527</v>
+        <v>77.51948971688309</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1009167292563729</v>
+        <v>0.1015125857888742</v>
       </c>
       <c r="T27">
-        <v>1.074327641920924</v>
+        <v>1.085941994806556</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.31236295062826</v>
+        <v>11.83881052945025</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08522031348376694</v>
+        <v>0.08504058002525418</v>
       </c>
       <c r="C28">
-        <v>283.6237244608714</v>
+        <v>280.051754007701</v>
       </c>
       <c r="D28">
-        <v>346.9987639233402</v>
+        <v>347.4566026802648</v>
       </c>
       <c r="E28">
-        <v>-271.5058815470265</v>
+        <v>-267.4760723369316</v>
       </c>
       <c r="F28">
-        <v>104.7750394624688</v>
+        <v>108.8048486725638</v>
       </c>
       <c r="G28">
         <v>41.4</v>
@@ -3577,28 +3577,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M28">
-        <v>5.427347044155883</v>
+        <v>5.636091161238802</v>
       </c>
       <c r="N28">
-        <v>58.82598628917745</v>
+        <v>58.61724217209453</v>
       </c>
       <c r="O28">
-        <v>14.70649657229436</v>
+        <v>14.65431054302363</v>
       </c>
       <c r="P28">
-        <v>44.11948971688309</v>
+        <v>43.96293162907089</v>
       </c>
       <c r="Q28">
-        <v>77.51948971688309</v>
+        <v>77.36293162907089</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1015125857888742</v>
+        <v>0.1021247671578824</v>
       </c>
       <c r="T28">
-        <v>1.085941994806556</v>
+        <v>1.097874549141109</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.83881052945025</v>
+        <v>11.40033606539653</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08504058002525418</v>
+        <v>0.08486084656674142</v>
       </c>
       <c r="C29">
-        <v>280.051754007701</v>
+        <v>276.4809933182967</v>
       </c>
       <c r="D29">
-        <v>347.4566026802648</v>
+        <v>347.9156512009554</v>
       </c>
       <c r="E29">
-        <v>-267.4760723369316</v>
+        <v>-263.4462631268366</v>
       </c>
       <c r="F29">
-        <v>108.8048486725638</v>
+        <v>112.8346578826587</v>
       </c>
       <c r="G29">
         <v>41.4</v>
@@ -3659,28 +3659,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M29">
-        <v>5.636091161238802</v>
+        <v>5.844835278321721</v>
       </c>
       <c r="N29">
-        <v>58.61724217209453</v>
+        <v>58.40849805501161</v>
       </c>
       <c r="O29">
-        <v>14.65431054302363</v>
+        <v>14.6021245137529</v>
       </c>
       <c r="P29">
-        <v>43.96293162907089</v>
+        <v>43.80637354125871</v>
       </c>
       <c r="Q29">
-        <v>77.36293162907089</v>
+        <v>77.2063735412587</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1021247671578824</v>
+        <v>0.1027539535649186</v>
       </c>
       <c r="T29">
-        <v>1.097874549141109</v>
+        <v>1.110138563318288</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.40033606539653</v>
+        <v>10.99318120591808</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08486084656674142</v>
+        <v>0.08468111310822868</v>
       </c>
       <c r="C30">
-        <v>276.4809933182967</v>
+        <v>272.9114471939047</v>
       </c>
       <c r="D30">
-        <v>347.9156512009554</v>
+        <v>348.3759142866584</v>
       </c>
       <c r="E30">
-        <v>-263.4462631268366</v>
+        <v>-259.4164539167417</v>
       </c>
       <c r="F30">
-        <v>112.8346578826587</v>
+        <v>116.8644670927537</v>
       </c>
       <c r="G30">
         <v>41.4</v>
@@ -3741,28 +3741,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M30">
-        <v>5.844835278321721</v>
+        <v>6.053579395404639</v>
       </c>
       <c r="N30">
-        <v>58.40849805501161</v>
+        <v>58.19975393792869</v>
       </c>
       <c r="O30">
-        <v>14.6021245137529</v>
+        <v>14.54993848448217</v>
       </c>
       <c r="P30">
-        <v>43.80637354125871</v>
+        <v>43.64981545344652</v>
       </c>
       <c r="Q30">
-        <v>77.2063735412587</v>
+        <v>77.04981545344651</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1027539535649186</v>
+        <v>0.1034008635327165</v>
       </c>
       <c r="T30">
-        <v>1.110138563318288</v>
+        <v>1.122748042683557</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.99318120591808</v>
+        <v>10.61410599192091</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08468111310822868</v>
+        <v>0.08450137964971594</v>
       </c>
       <c r="C31">
-        <v>272.9114471939047</v>
+        <v>269.3431204612119</v>
       </c>
       <c r="D31">
-        <v>348.3759142866584</v>
+        <v>348.8373967640605</v>
       </c>
       <c r="E31">
-        <v>-259.4164539167417</v>
+        <v>-255.3866447066467</v>
       </c>
       <c r="F31">
-        <v>116.8644670927536</v>
+        <v>120.8942763028486</v>
       </c>
       <c r="G31">
         <v>41.4</v>
@@ -3823,28 +3823,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M31">
-        <v>6.053579395404638</v>
+        <v>6.262323512487557</v>
       </c>
       <c r="N31">
-        <v>58.19975393792869</v>
+        <v>57.99100982084578</v>
       </c>
       <c r="O31">
-        <v>14.54993848448217</v>
+        <v>14.49775245521144</v>
       </c>
       <c r="P31">
-        <v>43.64981545344652</v>
+        <v>43.49325736563434</v>
       </c>
       <c r="Q31">
-        <v>77.04981545344651</v>
+        <v>76.89325736563433</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1034008635327165</v>
+        <v>0.1040662566424513</v>
       </c>
       <c r="T31">
-        <v>1.122748042683557</v>
+        <v>1.135717792887834</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.61410599192091</v>
+        <v>10.26030245885688</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08450137964971594</v>
+        <v>0.08432164619120319</v>
       </c>
       <c r="C32">
-        <v>269.3431204612119</v>
+        <v>265.7760179725142</v>
       </c>
       <c r="D32">
-        <v>348.8373967640605</v>
+        <v>349.3001034854577</v>
       </c>
       <c r="E32">
-        <v>-255.3866447066467</v>
+        <v>-251.3568354965518</v>
       </c>
       <c r="F32">
-        <v>120.8942763028486</v>
+        <v>124.9240855129435</v>
       </c>
       <c r="G32">
         <v>41.4</v>
@@ -3905,28 +3905,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M32">
-        <v>6.262323512487557</v>
+        <v>6.471067629570475</v>
       </c>
       <c r="N32">
-        <v>57.99100982084578</v>
+        <v>57.78226570376285</v>
       </c>
       <c r="O32">
-        <v>14.49775245521144</v>
+        <v>14.44556642594071</v>
       </c>
       <c r="P32">
-        <v>43.49325736563434</v>
+        <v>43.33669927782214</v>
       </c>
       <c r="Q32">
-        <v>76.89325736563433</v>
+        <v>76.73669927782214</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1040662566424513</v>
+        <v>0.1047509365089901</v>
       </c>
       <c r="T32">
-        <v>1.135717792887834</v>
+        <v>1.14906347788064</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.26030245885688</v>
+        <v>9.929324960184077</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08432164619120319</v>
+        <v>0.08454991273269044</v>
       </c>
       <c r="C33">
-        <v>265.7760179725142</v>
+        <v>261.1587683536528</v>
       </c>
       <c r="D33">
-        <v>349.3001034854577</v>
+        <v>348.7126630766913</v>
       </c>
       <c r="E33">
-        <v>-251.3568354965518</v>
+        <v>-247.3270262864568</v>
       </c>
       <c r="F33">
-        <v>124.9240855129435</v>
+        <v>128.9538947230385</v>
       </c>
       <c r="G33">
         <v>41.4</v>
@@ -3987,45 +3987,45 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M33">
-        <v>6.471067629570475</v>
+        <v>6.89903336768256</v>
       </c>
       <c r="N33">
-        <v>57.78226570376285</v>
+        <v>57.35429996565077</v>
       </c>
       <c r="O33">
-        <v>14.44556642594071</v>
+        <v>14.33857499141269</v>
       </c>
       <c r="P33">
-        <v>43.33669927782214</v>
+        <v>43.01572497423808</v>
       </c>
       <c r="Q33">
-        <v>76.73669927782214</v>
+        <v>76.41572497423807</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1047509365089901</v>
+        <v>0.1054557540186624</v>
       </c>
       <c r="T33">
-        <v>1.14906347788064</v>
+        <v>1.162801683020294</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>9.929324960184077</v>
+        <v>9.313382021649293</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08454991273269044</v>
+        <v>0.08438292927417769</v>
       </c>
       <c r="C34">
-        <v>261.1587683536528</v>
+        <v>257.5584942231998</v>
       </c>
       <c r="D34">
-        <v>348.7126630766913</v>
+        <v>349.1421981563332</v>
       </c>
       <c r="E34">
-        <v>-247.3270262864568</v>
+        <v>-243.2972170763619</v>
       </c>
       <c r="F34">
-        <v>128.9538947230385</v>
+        <v>132.9837039331335</v>
       </c>
       <c r="G34">
         <v>41.4</v>
@@ -4069,28 +4069,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M34">
-        <v>6.89903336768256</v>
+        <v>7.114628160422639</v>
       </c>
       <c r="N34">
-        <v>57.35429996565077</v>
+        <v>57.13870517291069</v>
       </c>
       <c r="O34">
-        <v>14.33857499141269</v>
+        <v>14.28467629322767</v>
       </c>
       <c r="P34">
-        <v>43.01572497423808</v>
+        <v>42.85402887968301</v>
       </c>
       <c r="Q34">
-        <v>76.41572497423807</v>
+        <v>76.25402887968301</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1054557540186624</v>
+        <v>0.1061816108569816</v>
       </c>
       <c r="T34">
-        <v>1.162801683020294</v>
+        <v>1.176949983835758</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.313382021649293</v>
+        <v>9.031158324023558</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08438292927417769</v>
+        <v>0.08421594581566495</v>
       </c>
       <c r="C35">
-        <v>257.5584942231998</v>
+        <v>253.9592795778024</v>
       </c>
       <c r="D35">
-        <v>349.1421981563332</v>
+        <v>349.5727927210309</v>
       </c>
       <c r="E35">
-        <v>-243.2972170763619</v>
+        <v>-239.2674078662669</v>
       </c>
       <c r="F35">
-        <v>132.9837039331335</v>
+        <v>137.0135131432284</v>
       </c>
       <c r="G35">
         <v>41.4</v>
@@ -4151,28 +4151,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M35">
-        <v>7.114628160422639</v>
+        <v>7.330222953162719</v>
       </c>
       <c r="N35">
-        <v>57.13870517291069</v>
+        <v>56.92311038017061</v>
       </c>
       <c r="O35">
-        <v>14.28467629322767</v>
+        <v>14.23077759504265</v>
       </c>
       <c r="P35">
-        <v>42.85402887968301</v>
+        <v>42.69233278512796</v>
       </c>
       <c r="Q35">
-        <v>76.25402887968301</v>
+        <v>76.09233278512795</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1061816108569816</v>
+        <v>0.1069294633570681</v>
       </c>
       <c r="T35">
-        <v>1.176949983835758</v>
+        <v>1.19152702103957</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.031158324023558</v>
+        <v>8.765536020375805</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08421594581566495</v>
+        <v>0.0840489623571522</v>
       </c>
       <c r="C36">
-        <v>253.9592795778024</v>
+        <v>250.3611283422672</v>
       </c>
       <c r="D36">
-        <v>349.5727927210309</v>
+        <v>350.0044506955906</v>
       </c>
       <c r="E36">
-        <v>-239.2674078662669</v>
+        <v>-235.237598656172</v>
       </c>
       <c r="F36">
-        <v>137.0135131432284</v>
+        <v>141.0433223533234</v>
       </c>
       <c r="G36">
         <v>41.4</v>
@@ -4233,28 +4233,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M36">
-        <v>7.330222953162719</v>
+        <v>7.5458177459028</v>
       </c>
       <c r="N36">
-        <v>56.92311038017061</v>
+        <v>56.70751558743053</v>
       </c>
       <c r="O36">
-        <v>14.23077759504265</v>
+        <v>14.17687889685763</v>
       </c>
       <c r="P36">
-        <v>42.69233278512796</v>
+        <v>42.5306366905729</v>
       </c>
       <c r="Q36">
-        <v>76.09233278512795</v>
+        <v>75.9306366905729</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1069294633570681</v>
+        <v>0.1077003267033111</v>
       </c>
       <c r="T36">
-        <v>1.19152702103957</v>
+        <v>1.206552582465038</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.765536020375805</v>
+        <v>8.515092134079353</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0840489623571522</v>
+        <v>0.08388197889863945</v>
       </c>
       <c r="C37">
-        <v>250.3611283422672</v>
+        <v>246.7640444608101</v>
       </c>
       <c r="D37">
-        <v>350.0044506955906</v>
+        <v>350.4371760242285</v>
       </c>
       <c r="E37">
-        <v>-235.237598656172</v>
+        <v>-231.207789446077</v>
       </c>
       <c r="F37">
-        <v>141.0433223533234</v>
+        <v>145.0731315634183</v>
       </c>
       <c r="G37">
         <v>41.4</v>
@@ -4315,28 +4315,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M37">
-        <v>7.5458177459028</v>
+        <v>7.761412538642881</v>
       </c>
       <c r="N37">
-        <v>56.70751558743053</v>
+        <v>56.49192079469045</v>
       </c>
       <c r="O37">
-        <v>14.17687889685763</v>
+        <v>14.12298019867261</v>
       </c>
       <c r="P37">
-        <v>42.5306366905729</v>
+        <v>42.36894059601784</v>
       </c>
       <c r="Q37">
-        <v>75.9306366905729</v>
+        <v>75.76894059601784</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1077003267033111</v>
+        <v>0.1084952795291242</v>
       </c>
       <c r="T37">
-        <v>1.206552582465038</v>
+        <v>1.222047692685051</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.515092134079353</v>
+        <v>8.278561797021592</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08388197889863946</v>
+        <v>0.08371499544012673</v>
       </c>
       <c r="C38">
-        <v>246.7640444608101</v>
+        <v>243.1680318971769</v>
       </c>
       <c r="D38">
-        <v>350.4371760242284</v>
+        <v>350.8709726706902</v>
       </c>
       <c r="E38">
-        <v>-231.207789446077</v>
+        <v>-227.1779802359821</v>
       </c>
       <c r="F38">
-        <v>145.0731315634183</v>
+        <v>149.1029407735133</v>
       </c>
       <c r="G38">
         <v>41.4</v>
@@ -4397,28 +4397,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M38">
-        <v>7.76141253864288</v>
+        <v>7.97700733138296</v>
       </c>
       <c r="N38">
-        <v>56.49192079469045</v>
+        <v>56.27632600195037</v>
       </c>
       <c r="O38">
-        <v>14.12298019867261</v>
+        <v>14.06908150048759</v>
       </c>
       <c r="P38">
-        <v>42.36894059601784</v>
+        <v>42.20724450146278</v>
       </c>
       <c r="Q38">
-        <v>75.76894059601784</v>
+        <v>75.60724450146279</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1084952795291242</v>
+        <v>0.1093154689525821</v>
       </c>
       <c r="T38">
-        <v>1.222047692685051</v>
+        <v>1.238034711166017</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.278561797021595</v>
+        <v>8.054816883588579</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08371499544012673</v>
+        <v>0.08354801198161396</v>
       </c>
       <c r="C39">
-        <v>243.1680318971769</v>
+        <v>239.5730946347639</v>
       </c>
       <c r="D39">
-        <v>350.8709726706902</v>
+        <v>351.3058446183722</v>
       </c>
       <c r="E39">
-        <v>-227.1779802359821</v>
+        <v>-223.1481710258871</v>
       </c>
       <c r="F39">
-        <v>149.1029407735133</v>
+        <v>153.1327499836082</v>
       </c>
       <c r="G39">
         <v>41.4</v>
@@ -4479,28 +4479,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M39">
-        <v>7.97700733138296</v>
+        <v>8.19260212412304</v>
       </c>
       <c r="N39">
-        <v>56.27632600195037</v>
+        <v>56.06073120921029</v>
       </c>
       <c r="O39">
-        <v>14.06908150048759</v>
+        <v>14.01518280230257</v>
       </c>
       <c r="P39">
-        <v>42.20724450146278</v>
+        <v>42.04554840690771</v>
       </c>
       <c r="Q39">
-        <v>75.60724450146279</v>
+        <v>75.4455484069077</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1093154689525821</v>
+        <v>0.1101621160993774</v>
       </c>
       <c r="T39">
-        <v>1.238034711166017</v>
+        <v>1.254537439920563</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.054816883588579</v>
+        <v>7.842848018230984</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08354801198161396</v>
+        <v>0.08338102852310122</v>
       </c>
       <c r="C40">
-        <v>239.5730946347639</v>
+        <v>235.9792366767406</v>
       </c>
       <c r="D40">
-        <v>351.3058446183722</v>
+        <v>351.7417958704438</v>
       </c>
       <c r="E40">
-        <v>-223.1481710258871</v>
+        <v>-219.1183618157922</v>
       </c>
       <c r="F40">
-        <v>153.1327499836082</v>
+        <v>157.1625591937032</v>
       </c>
       <c r="G40">
         <v>41.4</v>
@@ -4561,28 +4561,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M40">
-        <v>8.19260212412304</v>
+        <v>8.408196916863119</v>
       </c>
       <c r="N40">
-        <v>56.06073120921029</v>
+        <v>55.84513641647021</v>
       </c>
       <c r="O40">
-        <v>14.01518280230257</v>
+        <v>13.96128410411755</v>
       </c>
       <c r="P40">
-        <v>42.04554840690771</v>
+        <v>41.88385231235266</v>
       </c>
       <c r="Q40">
-        <v>75.4455484069077</v>
+        <v>75.28385231235265</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1101621160993774</v>
+        <v>0.1110365221690184</v>
       </c>
       <c r="T40">
-        <v>1.254537439920563</v>
+        <v>1.271581241749028</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.842848018230984</v>
+        <v>7.641749351096856</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08338102852310122</v>
+        <v>0.08345404506458848</v>
       </c>
       <c r="C41">
-        <v>235.9792366767406</v>
+        <v>231.7586668393898</v>
       </c>
       <c r="D41">
-        <v>351.7417958704438</v>
+        <v>351.5510352431879</v>
       </c>
       <c r="E41">
-        <v>-219.1183618157922</v>
+        <v>-215.0885526056972</v>
       </c>
       <c r="F41">
-        <v>157.1625591937032</v>
+        <v>161.1923684037981</v>
       </c>
       <c r="G41">
         <v>41.4</v>
@@ -4643,45 +4643,45 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M41">
-        <v>8.408196916863119</v>
+        <v>8.752745604326238</v>
       </c>
       <c r="N41">
-        <v>55.84513641647021</v>
+        <v>55.50058772900709</v>
       </c>
       <c r="O41">
-        <v>13.96128410411755</v>
+        <v>13.87514693225177</v>
       </c>
       <c r="P41">
-        <v>41.88385231235266</v>
+        <v>41.62544079675532</v>
       </c>
       <c r="Q41">
-        <v>75.28385231235265</v>
+        <v>75.02544079675532</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1110365221690184</v>
+        <v>0.1119400751076475</v>
       </c>
       <c r="T41">
-        <v>1.271581241749028</v>
+        <v>1.289193170305109</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.641749351096856</v>
+        <v>7.340934632165558</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08345404506458848</v>
+        <v>0.08329306160607573</v>
       </c>
       <c r="C42">
-        <v>231.7586668393898</v>
+        <v>228.1497128715097</v>
       </c>
       <c r="D42">
-        <v>351.5510352431879</v>
+        <v>351.9718904854028</v>
       </c>
       <c r="E42">
-        <v>-215.0885526056972</v>
+        <v>-211.0587433956022</v>
       </c>
       <c r="F42">
-        <v>161.1923684037981</v>
+        <v>165.2221776138931</v>
       </c>
       <c r="G42">
         <v>41.4</v>
@@ -4725,28 +4725,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M42">
-        <v>8.752745604326238</v>
+        <v>8.971564244434395</v>
       </c>
       <c r="N42">
-        <v>55.50058772900709</v>
+        <v>55.28176908889893</v>
       </c>
       <c r="O42">
-        <v>13.87514693225177</v>
+        <v>13.82044227222473</v>
       </c>
       <c r="P42">
-        <v>41.62544079675532</v>
+        <v>41.4613268166742</v>
       </c>
       <c r="Q42">
-        <v>75.02544079675532</v>
+        <v>74.86132681667419</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1119400751076475</v>
+        <v>0.1128742569594504</v>
       </c>
       <c r="T42">
-        <v>1.289193170305109</v>
+        <v>1.307402113388514</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.340934632165558</v>
+        <v>7.161887446015177</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08329306160607573</v>
+        <v>0.08313207814756299</v>
       </c>
       <c r="C43">
-        <v>228.1497128715097</v>
+        <v>224.5417677553034</v>
       </c>
       <c r="D43">
-        <v>351.9718904854028</v>
+        <v>352.3937545792915</v>
       </c>
       <c r="E43">
-        <v>-211.0587433956022</v>
+        <v>-207.0289341855073</v>
       </c>
       <c r="F43">
-        <v>165.2221776138931</v>
+        <v>169.2519868239881</v>
       </c>
       <c r="G43">
         <v>41.4</v>
@@ -4807,28 +4807,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M43">
-        <v>8.971564244434395</v>
+        <v>9.190382884542553</v>
       </c>
       <c r="N43">
-        <v>55.28176908889893</v>
+        <v>55.06295044879078</v>
       </c>
       <c r="O43">
-        <v>13.82044227222473</v>
+        <v>13.76573761219769</v>
       </c>
       <c r="P43">
-        <v>41.4613268166742</v>
+        <v>41.29721283659308</v>
       </c>
       <c r="Q43">
-        <v>74.86132681667419</v>
+        <v>74.69721283659308</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1128742569594504</v>
+        <v>0.1138406519785569</v>
       </c>
       <c r="T43">
-        <v>1.307402113388514</v>
+        <v>1.326238951061003</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.161887446015177</v>
+        <v>6.991366316348148</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.083132078147563</v>
+        <v>0.08297109468905026</v>
       </c>
       <c r="C44">
-        <v>224.5417677553035</v>
+        <v>220.9348351226719</v>
       </c>
       <c r="D44">
-        <v>352.3937545792915</v>
+        <v>352.8166311567549</v>
       </c>
       <c r="E44">
-        <v>-207.0289341855073</v>
+        <v>-202.9991249754123</v>
       </c>
       <c r="F44">
-        <v>169.251986823988</v>
+        <v>173.281796034083</v>
       </c>
       <c r="G44">
         <v>41.4</v>
@@ -4889,28 +4889,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M44">
-        <v>9.190382884542551</v>
+        <v>9.409201524650706</v>
       </c>
       <c r="N44">
-        <v>55.06295044879078</v>
+        <v>54.84413180868263</v>
       </c>
       <c r="O44">
-        <v>13.76573761219769</v>
+        <v>13.71103295217066</v>
       </c>
       <c r="P44">
-        <v>41.29721283659308</v>
+        <v>41.13309885651197</v>
       </c>
       <c r="Q44">
-        <v>74.69721283659308</v>
+        <v>74.53309885651197</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1138406519785569</v>
+        <v>0.114840955594825</v>
       </c>
       <c r="T44">
-        <v>1.326238951061003</v>
+        <v>1.34573673040621</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.991366316348149</v>
+        <v>6.828776402014472</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08297109468905026</v>
+        <v>0.0828101112305375</v>
       </c>
       <c r="C45">
-        <v>220.9348351226719</v>
+        <v>217.3289186229704</v>
       </c>
       <c r="D45">
-        <v>352.8166311567549</v>
+        <v>353.2405238671484</v>
       </c>
       <c r="E45">
-        <v>-202.9991249754123</v>
+        <v>-198.9693157653174</v>
       </c>
       <c r="F45">
-        <v>173.281796034083</v>
+        <v>177.3116052441779</v>
       </c>
       <c r="G45">
         <v>41.4</v>
@@ -4971,28 +4971,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M45">
-        <v>9.409201524650706</v>
+        <v>9.628020164758862</v>
       </c>
       <c r="N45">
-        <v>54.84413180868263</v>
+        <v>54.62531316857446</v>
       </c>
       <c r="O45">
-        <v>13.71103295217066</v>
+        <v>13.65632829214362</v>
       </c>
       <c r="P45">
-        <v>41.13309885651197</v>
+        <v>40.96898487643085</v>
       </c>
       <c r="Q45">
-        <v>74.53309885651197</v>
+        <v>74.36898487643086</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.114840955594825</v>
+        <v>0.1158769843402455</v>
       </c>
       <c r="T45">
-        <v>1.34573673040621</v>
+        <v>1.365930859013746</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.828776402014472</v>
+        <v>6.673576938332324</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0828101112305375</v>
+        <v>0.08264912777202475</v>
       </c>
       <c r="C46">
-        <v>217.3289186229704</v>
+        <v>213.7240219231133</v>
       </c>
       <c r="D46">
-        <v>353.2405238671484</v>
+        <v>353.6654363773862</v>
       </c>
       <c r="E46">
-        <v>-198.9693157653174</v>
+        <v>-194.9395065552224</v>
       </c>
       <c r="F46">
-        <v>177.3116052441779</v>
+        <v>181.3414144542729</v>
       </c>
       <c r="G46">
         <v>41.4</v>
@@ -5053,28 +5053,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M46">
-        <v>9.628020164758862</v>
+        <v>9.846838804867017</v>
       </c>
       <c r="N46">
-        <v>54.62531316857446</v>
+        <v>54.40649452846631</v>
       </c>
       <c r="O46">
-        <v>13.65632829214362</v>
+        <v>13.60162363211658</v>
       </c>
       <c r="P46">
-        <v>40.96898487643085</v>
+        <v>40.80487089634973</v>
       </c>
       <c r="Q46">
-        <v>74.36898487643086</v>
+        <v>74.20487089634973</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1158769843402455</v>
+        <v>0.1169506868582268</v>
       </c>
       <c r="T46">
-        <v>1.365930859013746</v>
+        <v>1.386859319570647</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.673576938332324</v>
+        <v>6.525275228591607</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08264912777202475</v>
+        <v>0.08248814431351201</v>
       </c>
       <c r="C47">
-        <v>213.7240219231133</v>
+        <v>210.1201487076801</v>
       </c>
       <c r="D47">
-        <v>353.6654363773862</v>
+        <v>354.0913723720479</v>
       </c>
       <c r="E47">
-        <v>-194.9395065552224</v>
+        <v>-190.9096973451275</v>
       </c>
       <c r="F47">
-        <v>181.3414144542729</v>
+        <v>185.3712236643678</v>
       </c>
       <c r="G47">
         <v>41.4</v>
@@ -5135,28 +5135,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M47">
-        <v>9.846838804867017</v>
+        <v>10.06565744497517</v>
       </c>
       <c r="N47">
-        <v>54.40649452846631</v>
+        <v>54.18767588835816</v>
       </c>
       <c r="O47">
-        <v>13.60162363211658</v>
+        <v>13.54691897208954</v>
       </c>
       <c r="P47">
-        <v>40.80487089634973</v>
+        <v>40.64075691626861</v>
       </c>
       <c r="Q47">
-        <v>74.20487089634973</v>
+        <v>74.04075691626861</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1169506868582268</v>
+        <v>0.1180641561361333</v>
       </c>
       <c r="T47">
-        <v>1.386859319570647</v>
+        <v>1.408562908296322</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.525275228591607</v>
+        <v>6.383421419274397</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08248814431351201</v>
+        <v>0.08232716085499926</v>
       </c>
       <c r="C48">
-        <v>210.1201487076801</v>
+        <v>206.5173026790215</v>
       </c>
       <c r="D48">
-        <v>354.0913723720479</v>
+        <v>354.5183355534843</v>
       </c>
       <c r="E48">
-        <v>-190.9096973451275</v>
+        <v>-186.8798881350325</v>
       </c>
       <c r="F48">
-        <v>185.3712236643678</v>
+        <v>189.4010328744628</v>
       </c>
       <c r="G48">
         <v>41.4</v>
@@ -5217,28 +5217,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M48">
-        <v>10.06565744497517</v>
+        <v>10.28447608508333</v>
       </c>
       <c r="N48">
-        <v>54.18767588835816</v>
+        <v>53.96885724825</v>
       </c>
       <c r="O48">
-        <v>13.54691897208954</v>
+        <v>13.4922143120625</v>
       </c>
       <c r="P48">
-        <v>40.64075691626861</v>
+        <v>40.4766429361875</v>
       </c>
       <c r="Q48">
-        <v>74.04075691626861</v>
+        <v>73.87664293618749</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1180641561361333</v>
+        <v>0.1192196431226401</v>
       </c>
       <c r="T48">
-        <v>1.408562908296322</v>
+        <v>1.431085500370136</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.383421419274397</v>
+        <v>6.247603942268559</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08232716085499926</v>
+        <v>0.08216617739648652</v>
       </c>
       <c r="C49">
-        <v>206.5173026790215</v>
+        <v>202.9154875573672</v>
       </c>
       <c r="D49">
-        <v>354.5183355534843</v>
+        <v>354.946329641925</v>
       </c>
       <c r="E49">
-        <v>-186.8798881350325</v>
+        <v>-182.8500789249375</v>
       </c>
       <c r="F49">
-        <v>189.4010328744628</v>
+        <v>193.4308420845578</v>
       </c>
       <c r="G49">
         <v>41.4</v>
@@ -5299,28 +5299,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M49">
-        <v>10.28447608508333</v>
+        <v>10.50329472519149</v>
       </c>
       <c r="N49">
-        <v>53.96885724825</v>
+        <v>53.75003860814184</v>
       </c>
       <c r="O49">
-        <v>13.4922143120625</v>
+        <v>13.43750965203546</v>
       </c>
       <c r="P49">
-        <v>40.4766429361875</v>
+        <v>40.31252895610638</v>
       </c>
       <c r="Q49">
-        <v>73.87664293618749</v>
+        <v>73.71252895610638</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1192196431226401</v>
+        <v>0.1204195719163202</v>
       </c>
       <c r="T49">
-        <v>1.431085500370136</v>
+        <v>1.454474345985251</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.247603942268559</v>
+        <v>6.11744552680463</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08216617739648652</v>
+        <v>0.08237269393797376</v>
       </c>
       <c r="C50">
-        <v>202.9154875573673</v>
+        <v>198.3368162148533</v>
       </c>
       <c r="D50">
-        <v>354.946329641925</v>
+        <v>354.397467509506</v>
       </c>
       <c r="E50">
-        <v>-182.8500789249376</v>
+        <v>-178.8202697148426</v>
       </c>
       <c r="F50">
-        <v>193.4308420845578</v>
+        <v>197.4606512946527</v>
       </c>
       <c r="G50">
         <v>41.4</v>
@@ -5381,45 +5381,45 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M50">
-        <v>10.50329472519149</v>
+        <v>10.91957401659429</v>
       </c>
       <c r="N50">
-        <v>53.75003860814184</v>
+        <v>53.33375931673903</v>
       </c>
       <c r="O50">
-        <v>13.43750965203546</v>
+        <v>13.33343982918476</v>
       </c>
       <c r="P50">
-        <v>40.31252895610638</v>
+        <v>40.00031948755428</v>
       </c>
       <c r="Q50">
-        <v>73.71252895610638</v>
+        <v>73.40031948755427</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1204195719163202</v>
+        <v>0.121666556741125</v>
       </c>
       <c r="T50">
-        <v>1.454474345985251</v>
+        <v>1.47878040123233</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.117445526804631</v>
+        <v>5.884234424867546</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08237269393797376</v>
+        <v>0.08221921047946101</v>
       </c>
       <c r="C51">
-        <v>198.3368162148533</v>
+        <v>194.7147601444964</v>
       </c>
       <c r="D51">
-        <v>354.397467509506</v>
+        <v>354.8052206492441</v>
       </c>
       <c r="E51">
-        <v>-178.8202697148426</v>
+        <v>-174.7904605047477</v>
       </c>
       <c r="F51">
-        <v>197.4606512946527</v>
+        <v>201.4904605047477</v>
       </c>
       <c r="G51">
         <v>41.4</v>
@@ -5463,28 +5463,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M51">
-        <v>10.91957401659429</v>
+        <v>11.14242246591255</v>
       </c>
       <c r="N51">
-        <v>53.33375931673903</v>
+        <v>53.11091086742078</v>
       </c>
       <c r="O51">
-        <v>13.33343982918476</v>
+        <v>13.2777277168552</v>
       </c>
       <c r="P51">
-        <v>40.00031948755428</v>
+        <v>39.83318315056559</v>
       </c>
       <c r="Q51">
-        <v>73.40031948755427</v>
+        <v>73.23318315056559</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.121666556741125</v>
+        <v>0.122963420958922</v>
       </c>
       <c r="T51">
-        <v>1.47878040123233</v>
+        <v>1.504058698689293</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.884234424867546</v>
+        <v>5.766549736370195</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08221921047946101</v>
+        <v>0.08206572702094828</v>
       </c>
       <c r="C52">
-        <v>194.7147601444964</v>
+        <v>191.0936434382861</v>
       </c>
       <c r="D52">
-        <v>354.8052206492441</v>
+        <v>355.2139131531287</v>
       </c>
       <c r="E52">
-        <v>-174.7904605047477</v>
+        <v>-170.7606512946527</v>
       </c>
       <c r="F52">
-        <v>201.4904605047477</v>
+        <v>205.5202697148426</v>
       </c>
       <c r="G52">
         <v>41.4</v>
@@ -5545,28 +5545,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M52">
-        <v>11.14242246591255</v>
+        <v>11.3652709152308</v>
       </c>
       <c r="N52">
-        <v>53.11091086742078</v>
+        <v>52.88806241810254</v>
       </c>
       <c r="O52">
-        <v>13.2777277168552</v>
+        <v>13.22201560452563</v>
       </c>
       <c r="P52">
-        <v>39.83318315056559</v>
+        <v>39.6660468135769</v>
       </c>
       <c r="Q52">
-        <v>73.23318315056559</v>
+        <v>73.06604681357689</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.122963420958922</v>
+        <v>0.1243132184100985</v>
       </c>
       <c r="T52">
-        <v>1.504058698689293</v>
+        <v>1.530368763389398</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.766549736370195</v>
+        <v>5.65348013369627</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08206572702094828</v>
+        <v>0.08191224356243554</v>
       </c>
       <c r="C53">
-        <v>191.0936434382861</v>
+        <v>187.4734693460659</v>
       </c>
       <c r="D53">
-        <v>355.2139131531287</v>
+        <v>355.6235482710035</v>
       </c>
       <c r="E53">
-        <v>-170.7606512946527</v>
+        <v>-166.7308420845578</v>
       </c>
       <c r="F53">
-        <v>205.5202697148426</v>
+        <v>209.5500789249376</v>
       </c>
       <c r="G53">
         <v>41.4</v>
@@ -5627,28 +5627,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M53">
-        <v>11.3652709152308</v>
+        <v>11.58811936454905</v>
       </c>
       <c r="N53">
-        <v>52.88806241810254</v>
+        <v>52.66521396878429</v>
       </c>
       <c r="O53">
-        <v>13.22201560452563</v>
+        <v>13.16630349219607</v>
       </c>
       <c r="P53">
-        <v>39.6660468135769</v>
+        <v>39.49891047658821</v>
       </c>
       <c r="Q53">
-        <v>73.06604681357689</v>
+        <v>72.89891047658821</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1243132184100985</v>
+        <v>0.1257192574217407</v>
       </c>
       <c r="T53">
-        <v>1.530368763389398</v>
+        <v>1.55777508078534</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.65348013369627</v>
+        <v>5.544759361894418</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08191224356243554</v>
+        <v>0.08175876010392279</v>
       </c>
       <c r="C54">
-        <v>187.4734693460659</v>
+        <v>183.8542411326875</v>
       </c>
       <c r="D54">
-        <v>355.6235482710035</v>
+        <v>356.0341292677201</v>
       </c>
       <c r="E54">
-        <v>-166.7308420845578</v>
+        <v>-162.7010328744628</v>
       </c>
       <c r="F54">
-        <v>209.5500789249376</v>
+        <v>213.5798881350325</v>
       </c>
       <c r="G54">
         <v>41.4</v>
@@ -5709,28 +5709,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M54">
-        <v>11.58811936454905</v>
+        <v>11.8109678138673</v>
       </c>
       <c r="N54">
-        <v>52.66521396878429</v>
+        <v>52.44236551946603</v>
       </c>
       <c r="O54">
-        <v>13.16630349219607</v>
+        <v>13.11059137986651</v>
       </c>
       <c r="P54">
-        <v>39.49891047658821</v>
+        <v>39.33177413959952</v>
       </c>
       <c r="Q54">
-        <v>72.89891047658821</v>
+        <v>72.73177413959952</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1257192574217407</v>
+        <v>0.1271851278806868</v>
       </c>
       <c r="T54">
-        <v>1.55777508078534</v>
+        <v>1.586347624453449</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.544759361894418</v>
+        <v>5.440141260726599</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08175876010392279</v>
+        <v>0.08160527664541004</v>
       </c>
       <c r="C55">
-        <v>183.8542411326875</v>
+        <v>180.2359620780978</v>
       </c>
       <c r="D55">
-        <v>356.0341292677201</v>
+        <v>356.4456594232253</v>
       </c>
       <c r="E55">
-        <v>-162.7010328744628</v>
+        <v>-158.6712236643678</v>
       </c>
       <c r="F55">
-        <v>213.5798881350325</v>
+        <v>217.6096973451275</v>
       </c>
       <c r="G55">
         <v>41.4</v>
@@ -5791,28 +5791,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M55">
-        <v>11.8109678138673</v>
+        <v>12.03381626318555</v>
       </c>
       <c r="N55">
-        <v>52.44236551946603</v>
+        <v>52.21951707014778</v>
       </c>
       <c r="O55">
-        <v>13.11059137986651</v>
+        <v>13.05487926753695</v>
       </c>
       <c r="P55">
-        <v>39.33177413959952</v>
+        <v>39.16463780261083</v>
       </c>
       <c r="Q55">
-        <v>72.73177413959952</v>
+        <v>72.56463780261083</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1271851278806868</v>
+        <v>0.1287147318378479</v>
       </c>
       <c r="T55">
-        <v>1.586347624453449</v>
+        <v>1.616162452628868</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.440141260726599</v>
+        <v>5.339397904046476</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08160527664541004</v>
+        <v>0.0814517931868973</v>
       </c>
       <c r="C56">
-        <v>180.2359620780978</v>
+        <v>176.6186354774258</v>
       </c>
       <c r="D56">
-        <v>356.4456594232253</v>
+        <v>356.8581420326483</v>
       </c>
       <c r="E56">
-        <v>-158.6712236643678</v>
+        <v>-154.6414144542729</v>
       </c>
       <c r="F56">
-        <v>217.6096973451275</v>
+        <v>221.6395065552225</v>
       </c>
       <c r="G56">
         <v>41.4</v>
@@ -5873,28 +5873,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M56">
-        <v>12.03381626318555</v>
+        <v>12.2566647125038</v>
       </c>
       <c r="N56">
-        <v>52.21951707014778</v>
+        <v>51.99666862082952</v>
       </c>
       <c r="O56">
-        <v>13.05487926753695</v>
+        <v>12.99916715520738</v>
       </c>
       <c r="P56">
-        <v>39.16463780261083</v>
+        <v>38.99750146562214</v>
       </c>
       <c r="Q56">
-        <v>72.56463780261083</v>
+        <v>72.39750146562214</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1287147318378479</v>
+        <v>0.1303123181931051</v>
       </c>
       <c r="T56">
-        <v>1.616162452628868</v>
+        <v>1.64730238427875</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.339397904046476</v>
+        <v>5.242317942154721</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0814517931868973</v>
+        <v>0.08129830972838455</v>
       </c>
       <c r="C57">
-        <v>176.6186354774258</v>
+        <v>173.0022646410712</v>
       </c>
       <c r="D57">
-        <v>356.8581420326483</v>
+        <v>357.2715804063886</v>
       </c>
       <c r="E57">
-        <v>-154.6414144542729</v>
+        <v>-150.6116052441779</v>
       </c>
       <c r="F57">
-        <v>221.6395065552225</v>
+        <v>225.6693157653174</v>
       </c>
       <c r="G57">
         <v>41.4</v>
@@ -5955,28 +5955,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M57">
-        <v>12.2566647125038</v>
+        <v>12.47951316182205</v>
       </c>
       <c r="N57">
-        <v>51.99666862082952</v>
+        <v>51.77382017151128</v>
       </c>
       <c r="O57">
-        <v>12.99916715520738</v>
+        <v>12.94345504287782</v>
       </c>
       <c r="P57">
-        <v>38.99750146562214</v>
+        <v>38.83036512863346</v>
       </c>
       <c r="Q57">
-        <v>72.39750146562214</v>
+        <v>72.23036512863345</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1303123181931051</v>
+        <v>0.1319825221099649</v>
       </c>
       <c r="T57">
-        <v>1.64730238427875</v>
+        <v>1.679857767367263</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.242317942154721</v>
+        <v>5.148705121759102</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08129830972838455</v>
+        <v>0.08114482626987179</v>
       </c>
       <c r="C58">
-        <v>173.0022646410712</v>
+        <v>169.3868528947921</v>
       </c>
       <c r="D58">
-        <v>357.2715804063886</v>
+        <v>357.6859778702045</v>
       </c>
       <c r="E58">
-        <v>-150.6116052441779</v>
+        <v>-146.581796034083</v>
       </c>
       <c r="F58">
-        <v>225.6693157653174</v>
+        <v>229.6991249754124</v>
       </c>
       <c r="G58">
         <v>41.4</v>
@@ -6037,28 +6037,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M58">
-        <v>12.47951316182205</v>
+        <v>12.7023616111403</v>
       </c>
       <c r="N58">
-        <v>51.77382017151128</v>
+        <v>51.55097172219303</v>
       </c>
       <c r="O58">
-        <v>12.94345504287782</v>
+        <v>12.88774293054826</v>
       </c>
       <c r="P58">
-        <v>38.83036512863346</v>
+        <v>38.66322879164477</v>
       </c>
       <c r="Q58">
-        <v>72.23036512863345</v>
+        <v>72.06322879164478</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1319825221099649</v>
+        <v>0.1337304099299344</v>
       </c>
       <c r="T58">
-        <v>1.679857767367263</v>
+        <v>1.713927354320358</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.148705121759102</v>
+        <v>5.05837696172824</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08114482626987179</v>
+        <v>0.08099134281135906</v>
       </c>
       <c r="C59">
-        <v>169.3868528947921</v>
+        <v>165.7724035797948</v>
       </c>
       <c r="D59">
-        <v>357.6859778702045</v>
+        <v>358.1013377653021</v>
       </c>
       <c r="E59">
-        <v>-146.581796034083</v>
+        <v>-142.551986823988</v>
       </c>
       <c r="F59">
-        <v>229.6991249754124</v>
+        <v>233.7289341855073</v>
       </c>
       <c r="G59">
         <v>41.4</v>
@@ -6119,28 +6119,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M59">
-        <v>12.7023616111403</v>
+        <v>12.92521006045856</v>
       </c>
       <c r="N59">
-        <v>51.55097172219303</v>
+        <v>51.32812327287478</v>
       </c>
       <c r="O59">
-        <v>12.88774293054826</v>
+        <v>12.83203081821869</v>
       </c>
       <c r="P59">
-        <v>38.66322879164477</v>
+        <v>38.49609245465608</v>
       </c>
       <c r="Q59">
-        <v>72.06322879164478</v>
+        <v>71.89609245465607</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1337304099299344</v>
+        <v>0.1355615305032359</v>
       </c>
       <c r="T59">
-        <v>1.713927354320358</v>
+        <v>1.749619302556933</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.05837696172824</v>
+        <v>4.971163565836374</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08099134281135906</v>
+        <v>0.08083785935284631</v>
       </c>
       <c r="C60">
-        <v>165.7724035797948</v>
+        <v>162.1589200528237</v>
       </c>
       <c r="D60">
-        <v>358.1013377653021</v>
+        <v>358.5176634484259</v>
       </c>
       <c r="E60">
-        <v>-142.5519868239881</v>
+        <v>-138.5221776138931</v>
       </c>
       <c r="F60">
-        <v>233.7289341855073</v>
+        <v>237.7587433956022</v>
       </c>
       <c r="G60">
         <v>41.4</v>
@@ -6201,28 +6201,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M60">
-        <v>12.92521006045855</v>
+        <v>13.1480585097768</v>
       </c>
       <c r="N60">
-        <v>51.32812327287478</v>
+        <v>51.10527482355653</v>
       </c>
       <c r="O60">
-        <v>12.83203081821869</v>
+        <v>12.77631870588913</v>
       </c>
       <c r="P60">
-        <v>38.49609245465608</v>
+        <v>38.3289561176674</v>
       </c>
       <c r="Q60">
-        <v>71.89609245465607</v>
+        <v>71.72895611766739</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1355615305032359</v>
+        <v>0.1374819740313324</v>
       </c>
       <c r="T60">
-        <v>1.749619302556933</v>
+        <v>1.787052321439195</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.971163565836376</v>
+        <v>4.886906556245928</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08083785935284631</v>
+        <v>0.08068437589433357</v>
       </c>
       <c r="C61">
-        <v>162.1589200528237</v>
+        <v>158.546405686251</v>
       </c>
       <c r="D61">
-        <v>358.5176634484259</v>
+        <v>358.9349582919482</v>
       </c>
       <c r="E61">
-        <v>-138.5221776138931</v>
+        <v>-134.4923684037981</v>
       </c>
       <c r="F61">
-        <v>237.7587433956022</v>
+        <v>241.7885526056972</v>
       </c>
       <c r="G61">
         <v>41.4</v>
@@ -6283,28 +6283,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M61">
-        <v>13.1480585097768</v>
+        <v>13.37090695909506</v>
       </c>
       <c r="N61">
-        <v>51.10527482355653</v>
+        <v>50.88242637423828</v>
       </c>
       <c r="O61">
-        <v>12.77631870588913</v>
+        <v>12.72060659355957</v>
       </c>
       <c r="P61">
-        <v>38.3289561176674</v>
+        <v>38.16181978067871</v>
       </c>
       <c r="Q61">
-        <v>71.72895611766739</v>
+        <v>71.56181978067872</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1374819740313324</v>
+        <v>0.1394984397358339</v>
       </c>
       <c r="T61">
-        <v>1.787052321439195</v>
+        <v>1.826356991265571</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.886906556245928</v>
+        <v>4.80545811364183</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08068437589433357</v>
+        <v>0.08053089243582083</v>
       </c>
       <c r="C62">
-        <v>158.546405686251</v>
+        <v>154.9348638681687</v>
       </c>
       <c r="D62">
-        <v>358.9349582919482</v>
+        <v>359.3532256839608</v>
       </c>
       <c r="E62">
-        <v>-134.4923684037981</v>
+        <v>-130.4625591937032</v>
       </c>
       <c r="F62">
-        <v>241.7885526056972</v>
+        <v>245.8183618157921</v>
       </c>
       <c r="G62">
         <v>41.4</v>
@@ -6365,28 +6365,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M62">
-        <v>13.37090695909506</v>
+        <v>13.59375540841331</v>
       </c>
       <c r="N62">
-        <v>50.88242637423828</v>
+        <v>50.65957792492002</v>
       </c>
       <c r="O62">
-        <v>12.72060659355957</v>
+        <v>12.66489448123001</v>
       </c>
       <c r="P62">
-        <v>38.16181978067871</v>
+        <v>37.99468344369001</v>
       </c>
       <c r="Q62">
-        <v>71.56181978067872</v>
+        <v>71.39468344369001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1394984397358339</v>
+        <v>0.1416183139380021</v>
       </c>
       <c r="T62">
-        <v>1.826356991265571</v>
+        <v>1.867677285185606</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.80545811364183</v>
+        <v>4.726680111778848</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08053089243582083</v>
+        <v>0.08037740897730808</v>
       </c>
       <c r="C63">
-        <v>154.9348638681687</v>
+        <v>151.3242980024795</v>
       </c>
       <c r="D63">
-        <v>359.3532256839608</v>
+        <v>359.7724690283666</v>
       </c>
       <c r="E63">
-        <v>-130.4625591937032</v>
+        <v>-126.4327499836082</v>
       </c>
       <c r="F63">
-        <v>245.8183618157921</v>
+        <v>249.8481710258871</v>
       </c>
       <c r="G63">
         <v>41.4</v>
@@ -6447,28 +6447,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M63">
-        <v>13.59375540841331</v>
+        <v>13.81660385773156</v>
       </c>
       <c r="N63">
-        <v>50.65957792492002</v>
+        <v>50.43672947560177</v>
       </c>
       <c r="O63">
-        <v>12.66489448123001</v>
+        <v>12.60918236890044</v>
       </c>
       <c r="P63">
-        <v>37.99468344369001</v>
+        <v>37.82754710670133</v>
       </c>
       <c r="Q63">
-        <v>71.39468344369001</v>
+        <v>71.22754710670134</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1416183139380021</v>
+        <v>0.1438497604666002</v>
       </c>
       <c r="T63">
-        <v>1.867677285185606</v>
+        <v>1.911172331417222</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.726680111778848</v>
+        <v>4.650443335782415</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08037740897730808</v>
+        <v>0.08022392551879533</v>
       </c>
       <c r="C64">
-        <v>151.3242980024795</v>
+        <v>147.7147115089894</v>
       </c>
       <c r="D64">
-        <v>359.7724690283666</v>
+        <v>360.1926917449715</v>
       </c>
       <c r="E64">
-        <v>-126.4327499836082</v>
+        <v>-122.4029407735133</v>
       </c>
       <c r="F64">
-        <v>249.8481710258871</v>
+        <v>253.8779802359821</v>
       </c>
       <c r="G64">
         <v>41.4</v>
@@ -6529,28 +6529,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M64">
-        <v>13.81660385773156</v>
+        <v>14.03945230704981</v>
       </c>
       <c r="N64">
-        <v>50.43672947560177</v>
+        <v>50.21388102628352</v>
       </c>
       <c r="O64">
-        <v>12.60918236890044</v>
+        <v>12.55347025657088</v>
       </c>
       <c r="P64">
-        <v>37.82754710670133</v>
+        <v>37.66041076971264</v>
       </c>
       <c r="Q64">
-        <v>71.22754710670134</v>
+        <v>71.06041076971263</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1438497604666002</v>
+        <v>0.1462018257264739</v>
       </c>
       <c r="T64">
-        <v>1.911172331417222</v>
+        <v>1.957018461228926</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.650443335782415</v>
+        <v>4.57662677489698</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08022392551879533</v>
+        <v>0.08007044206028258</v>
       </c>
       <c r="C65">
-        <v>147.7147115089894</v>
+        <v>144.1061078235011</v>
       </c>
       <c r="D65">
-        <v>360.1926917449715</v>
+        <v>360.6138972695782</v>
       </c>
       <c r="E65">
-        <v>-122.4029407735133</v>
+        <v>-118.3731315634183</v>
       </c>
       <c r="F65">
-        <v>253.8779802359821</v>
+        <v>257.907789446077</v>
       </c>
       <c r="G65">
         <v>41.4</v>
@@ -6611,28 +6611,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M65">
-        <v>14.03945230704981</v>
+        <v>14.26230075636806</v>
       </c>
       <c r="N65">
-        <v>50.21388102628352</v>
+        <v>49.99103257696527</v>
       </c>
       <c r="O65">
-        <v>12.55347025657088</v>
+        <v>12.49775814424132</v>
       </c>
       <c r="P65">
-        <v>37.66041076971264</v>
+        <v>37.49327443272395</v>
       </c>
       <c r="Q65">
-        <v>71.06041076971263</v>
+        <v>70.89327443272396</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1462018257264739</v>
+        <v>0.1486845612785627</v>
       </c>
       <c r="T65">
-        <v>1.957018461228926</v>
+        <v>2.005411598252391</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.57662677489698</v>
+        <v>4.505116981539214</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08007044206028258</v>
+        <v>0.08113570860176983</v>
       </c>
       <c r="C66">
-        <v>144.1061078235011</v>
+        <v>137.1730267018452</v>
       </c>
       <c r="D66">
-        <v>360.6138972695782</v>
+        <v>357.7106253580172</v>
       </c>
       <c r="E66">
-        <v>-118.3731315634183</v>
+        <v>-114.3433223533233</v>
       </c>
       <c r="F66">
-        <v>257.907789446077</v>
+        <v>261.937598656172</v>
       </c>
       <c r="G66">
         <v>41.4</v>
@@ -6693,45 +6693,45 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M66">
-        <v>14.26230075636806</v>
+        <v>15.13999320232674</v>
       </c>
       <c r="N66">
-        <v>49.99103257696527</v>
+        <v>49.11334013100659</v>
       </c>
       <c r="O66">
-        <v>12.49775814424132</v>
+        <v>12.27833503275165</v>
       </c>
       <c r="P66">
-        <v>37.49327443272395</v>
+        <v>36.83500509825494</v>
       </c>
       <c r="Q66">
-        <v>70.89327443272396</v>
+        <v>70.23500509825493</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1486845612785627</v>
+        <v>0.1513091674336281</v>
       </c>
       <c r="T66">
-        <v>2.005411598252391</v>
+        <v>2.056570057391483</v>
       </c>
       <c r="U66">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.505116981539214</v>
+        <v>4.243947303982855</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08113570860176983</v>
+        <v>0.08100097514325709</v>
       </c>
       <c r="C67">
-        <v>137.1730267018452</v>
+        <v>133.5078343281612</v>
       </c>
       <c r="D67">
-        <v>357.7106253580172</v>
+        <v>358.0752421944281</v>
       </c>
       <c r="E67">
-        <v>-114.3433223533233</v>
+        <v>-110.3135131432284</v>
       </c>
       <c r="F67">
-        <v>261.937598656172</v>
+        <v>265.9674078662669</v>
       </c>
       <c r="G67">
         <v>41.4</v>
@@ -6775,28 +6775,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M67">
-        <v>15.13999320232674</v>
+        <v>15.37291617467023</v>
       </c>
       <c r="N67">
-        <v>49.11334013100659</v>
+        <v>48.8804171586631</v>
       </c>
       <c r="O67">
-        <v>12.27833503275165</v>
+        <v>12.22010428966577</v>
       </c>
       <c r="P67">
-        <v>36.83500509825494</v>
+        <v>36.66031286899732</v>
       </c>
       <c r="Q67">
-        <v>70.23500509825493</v>
+        <v>70.06031286899733</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1513091674336281</v>
+        <v>0.1540881621860503</v>
       </c>
       <c r="T67">
-        <v>2.056570057391483</v>
+        <v>2.110737837656404</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.243947303982855</v>
+        <v>4.179645072104327</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08100097514325709</v>
+        <v>0.08086624168474434</v>
       </c>
       <c r="C68">
-        <v>133.5078343281612</v>
+        <v>129.8433860256812</v>
       </c>
       <c r="D68">
-        <v>358.0752421944281</v>
+        <v>358.4406031020431</v>
       </c>
       <c r="E68">
-        <v>-110.3135131432284</v>
+        <v>-106.2837039331334</v>
       </c>
       <c r="F68">
-        <v>265.9674078662669</v>
+        <v>269.9972170763619</v>
       </c>
       <c r="G68">
         <v>41.4</v>
@@ -6857,28 +6857,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M68">
-        <v>15.37291617467023</v>
+        <v>15.60583914701372</v>
       </c>
       <c r="N68">
-        <v>48.8804171586631</v>
+        <v>48.64749418631961</v>
       </c>
       <c r="O68">
-        <v>12.22010428966577</v>
+        <v>12.1618735465799</v>
       </c>
       <c r="P68">
-        <v>36.66031286899732</v>
+        <v>36.48562063973971</v>
       </c>
       <c r="Q68">
-        <v>70.06031286899733</v>
+        <v>69.8856206397397</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1540881621860503</v>
+        <v>0.1570355808628617</v>
       </c>
       <c r="T68">
-        <v>2.110737837656404</v>
+        <v>2.168188513694956</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.179645072104327</v>
+        <v>4.117262309834113</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08086624168474434</v>
+        <v>0.0807315082262316</v>
       </c>
       <c r="C69">
-        <v>129.8433860256812</v>
+        <v>126.1796840743634</v>
       </c>
       <c r="D69">
-        <v>358.4406031020431</v>
+        <v>358.8067103608202</v>
       </c>
       <c r="E69">
-        <v>-106.2837039331334</v>
+        <v>-102.2538947230385</v>
       </c>
       <c r="F69">
-        <v>269.9972170763619</v>
+        <v>274.0270262864568</v>
       </c>
       <c r="G69">
         <v>41.4</v>
@@ -6939,28 +6939,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M69">
-        <v>15.60583914701372</v>
+        <v>15.83876211935721</v>
       </c>
       <c r="N69">
-        <v>48.64749418631961</v>
+        <v>48.41457121397612</v>
       </c>
       <c r="O69">
-        <v>12.1618735465799</v>
+        <v>12.10364280349403</v>
       </c>
       <c r="P69">
-        <v>36.48562063973971</v>
+        <v>36.31092841048209</v>
       </c>
       <c r="Q69">
-        <v>69.8856206397397</v>
+        <v>69.7109284104821</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1570355808628617</v>
+        <v>0.1601672132069738</v>
       </c>
       <c r="T69">
-        <v>2.168188513694956</v>
+        <v>2.229229856985917</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.117262309834113</v>
+        <v>4.056714334689494</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0807315082262316</v>
+        <v>0.08240802476771884</v>
       </c>
       <c r="C70">
-        <v>126.1796840743634</v>
+        <v>117.6469027273054</v>
       </c>
       <c r="D70">
-        <v>358.8067103608202</v>
+        <v>354.3037382238572</v>
       </c>
       <c r="E70">
-        <v>-102.2538947230385</v>
+        <v>-98.22408551294353</v>
       </c>
       <c r="F70">
-        <v>274.0270262864568</v>
+        <v>278.0568354965518</v>
       </c>
       <c r="G70">
         <v>41.4</v>
@@ -7021,45 +7021,45 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M70">
-        <v>15.83876211935721</v>
+        <v>17.04488401593862</v>
       </c>
       <c r="N70">
-        <v>48.41457121397612</v>
+        <v>47.20844931739471</v>
       </c>
       <c r="O70">
-        <v>12.10364280349403</v>
+        <v>11.80211232934868</v>
       </c>
       <c r="P70">
-        <v>36.31092841048209</v>
+        <v>35.40633698804604</v>
       </c>
       <c r="Q70">
-        <v>69.7109284104821</v>
+        <v>68.80633698804604</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1601672132069738</v>
+        <v>0.1635008863474802</v>
       </c>
       <c r="T70">
-        <v>2.229229856985917</v>
+        <v>2.294209351456941</v>
       </c>
       <c r="U70">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.056714334689494</v>
+        <v>3.76965506325829</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08240802476771884</v>
+        <v>0.08229954130920611</v>
       </c>
       <c r="C71">
-        <v>117.6469027273054</v>
+        <v>113.9050473998377</v>
       </c>
       <c r="D71">
-        <v>354.3037382238572</v>
+        <v>354.5916921064845</v>
       </c>
       <c r="E71">
-        <v>-98.22408551294353</v>
+        <v>-94.19427630284861</v>
       </c>
       <c r="F71">
-        <v>278.0568354965518</v>
+        <v>282.0866447066467</v>
       </c>
       <c r="G71">
         <v>41.4</v>
@@ -7103,28 +7103,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M71">
-        <v>17.04488401593862</v>
+        <v>17.29191132051744</v>
       </c>
       <c r="N71">
-        <v>47.20844931739471</v>
+        <v>46.96142201281589</v>
       </c>
       <c r="O71">
-        <v>11.80211232934868</v>
+        <v>11.74035550320397</v>
       </c>
       <c r="P71">
-        <v>35.40633698804604</v>
+        <v>35.22106650961192</v>
       </c>
       <c r="Q71">
-        <v>68.80633698804604</v>
+        <v>68.62106650961192</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1635008863474802</v>
+        <v>0.1670568043640204</v>
       </c>
       <c r="T71">
-        <v>2.294209351456941</v>
+        <v>2.363520812226033</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.76965506325829</v>
+        <v>3.715802848068886</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08229954130920611</v>
+        <v>0.08219105785069336</v>
       </c>
       <c r="C72">
-        <v>113.9050473998377</v>
+        <v>110.1636605115876</v>
       </c>
       <c r="D72">
-        <v>354.5916921064845</v>
+        <v>354.8801144283294</v>
       </c>
       <c r="E72">
-        <v>-94.19427630284861</v>
+        <v>-90.16446709275363</v>
       </c>
       <c r="F72">
-        <v>282.0866447066467</v>
+        <v>286.1164539167417</v>
       </c>
       <c r="G72">
         <v>41.4</v>
@@ -7185,28 +7185,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M72">
-        <v>17.29191132051744</v>
+        <v>17.53893862509627</v>
       </c>
       <c r="N72">
-        <v>46.96142201281589</v>
+        <v>46.71439470823707</v>
       </c>
       <c r="O72">
-        <v>11.74035550320397</v>
+        <v>11.67859867705927</v>
       </c>
       <c r="P72">
-        <v>35.22106650961192</v>
+        <v>35.0357960311778</v>
       </c>
       <c r="Q72">
-        <v>68.62106650961192</v>
+        <v>68.4357960311778</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1670568043640204</v>
+        <v>0.1708579581058392</v>
       </c>
       <c r="T72">
-        <v>2.363520812226033</v>
+        <v>2.437612373737821</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.715802848068886</v>
+        <v>3.663467596687634</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08219105785069336</v>
+        <v>0.08208257439218061</v>
       </c>
       <c r="C73">
-        <v>110.1636605115877</v>
+        <v>106.4227432065609</v>
       </c>
       <c r="D73">
-        <v>354.8801144283294</v>
+        <v>355.1690063333976</v>
       </c>
       <c r="E73">
-        <v>-90.16446709275368</v>
+        <v>-86.1346578826587</v>
       </c>
       <c r="F73">
-        <v>286.1164539167416</v>
+        <v>290.1462631268366</v>
       </c>
       <c r="G73">
         <v>41.4</v>
@@ -7267,28 +7267,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M73">
-        <v>17.53893862509626</v>
+        <v>17.78596592967509</v>
       </c>
       <c r="N73">
-        <v>46.71439470823707</v>
+        <v>46.46736740365824</v>
       </c>
       <c r="O73">
-        <v>11.67859867705927</v>
+        <v>11.61684185091456</v>
       </c>
       <c r="P73">
-        <v>35.0357960311778</v>
+        <v>34.85052555274368</v>
       </c>
       <c r="Q73">
-        <v>68.4357960311778</v>
+        <v>68.25052555274368</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1708579581058392</v>
+        <v>0.1749306228292165</v>
       </c>
       <c r="T73">
-        <v>2.43761237373782</v>
+        <v>2.516996189643307</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.663467596687634</v>
+        <v>3.612586102289195</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08208257439218061</v>
+        <v>0.08197409093366786</v>
       </c>
       <c r="C74">
-        <v>106.4227432065609</v>
+        <v>102.6822966324916</v>
       </c>
       <c r="D74">
-        <v>355.1690063333976</v>
+        <v>355.4583689694231</v>
       </c>
       <c r="E74">
-        <v>-86.1346578826587</v>
+        <v>-82.10484867256378</v>
       </c>
       <c r="F74">
-        <v>290.1462631268366</v>
+        <v>294.1760723369316</v>
       </c>
       <c r="G74">
         <v>41.4</v>
@@ -7349,28 +7349,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M74">
-        <v>17.78596592967509</v>
+        <v>18.0329932342539</v>
       </c>
       <c r="N74">
-        <v>46.46736740365824</v>
+        <v>46.22034009907942</v>
       </c>
       <c r="O74">
-        <v>11.61684185091456</v>
+        <v>11.55508502476986</v>
       </c>
       <c r="P74">
-        <v>34.85052555274368</v>
+        <v>34.66525507430957</v>
       </c>
       <c r="Q74">
-        <v>68.25052555274368</v>
+        <v>68.06525507430956</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1749306228292165</v>
+        <v>0.1793049664209921</v>
       </c>
       <c r="T74">
-        <v>2.516996189643307</v>
+        <v>2.60226028820846</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.612586102289195</v>
+        <v>3.563098621435918</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08197409093366786</v>
+        <v>0.08186560747515513</v>
       </c>
       <c r="C75">
-        <v>102.6822966324916</v>
+        <v>98.94232194085674</v>
       </c>
       <c r="D75">
-        <v>355.4583689694231</v>
+        <v>355.7482034878833</v>
       </c>
       <c r="E75">
-        <v>-82.10484867256378</v>
+        <v>-78.07503946246879</v>
       </c>
       <c r="F75">
-        <v>294.1760723369316</v>
+        <v>298.2058815470265</v>
       </c>
       <c r="G75">
         <v>41.4</v>
@@ -7431,28 +7431,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M75">
-        <v>18.0329932342539</v>
+        <v>18.28002053883273</v>
       </c>
       <c r="N75">
-        <v>46.22034009907942</v>
+        <v>45.9733127945006</v>
       </c>
       <c r="O75">
-        <v>11.55508502476986</v>
+        <v>11.49332819862515</v>
       </c>
       <c r="P75">
-        <v>34.66525507430957</v>
+        <v>34.47998459587545</v>
       </c>
       <c r="Q75">
-        <v>68.06525507430956</v>
+        <v>67.87998459587544</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1793049664209921</v>
+        <v>0.1840157979813659</v>
       </c>
       <c r="T75">
-        <v>2.60226028820846</v>
+        <v>2.694083163586316</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.563098621435918</v>
+        <v>3.514948640065162</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08186560747515513</v>
+        <v>0.08333212401664239</v>
       </c>
       <c r="C76">
-        <v>98.94232194085674</v>
+        <v>91.03398723304207</v>
       </c>
       <c r="D76">
-        <v>355.7482034878833</v>
+        <v>351.8696779901636</v>
       </c>
       <c r="E76">
-        <v>-78.07503946246879</v>
+        <v>-74.04523025237387</v>
       </c>
       <c r="F76">
-        <v>298.2058815470265</v>
+        <v>302.2356907571215</v>
       </c>
       <c r="G76">
         <v>41.4</v>
@@ -7513,45 +7513,45 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M76">
-        <v>18.28002053883273</v>
+        <v>19.37330777753149</v>
       </c>
       <c r="N76">
-        <v>45.9733127945006</v>
+        <v>44.88002555580184</v>
       </c>
       <c r="O76">
-        <v>11.49332819862515</v>
+        <v>11.22000638895046</v>
       </c>
       <c r="P76">
-        <v>34.47998459587545</v>
+        <v>33.66001916685138</v>
       </c>
       <c r="Q76">
-        <v>67.87998459587544</v>
+        <v>67.06001916685139</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1840157979813659</v>
+        <v>0.1891034960665695</v>
       </c>
       <c r="T76">
-        <v>2.694083163586316</v>
+        <v>2.793251868994402</v>
       </c>
       <c r="U76">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.514948640065162</v>
+        <v>3.316590748011147</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08333212401664239</v>
+        <v>0.08324464055812963</v>
       </c>
       <c r="C77">
-        <v>91.03398723304207</v>
+        <v>87.23317370970568</v>
       </c>
       <c r="D77">
-        <v>351.8696779901636</v>
+        <v>352.0986736769221</v>
       </c>
       <c r="E77">
-        <v>-74.04523025237387</v>
+        <v>-70.01542104227889</v>
       </c>
       <c r="F77">
-        <v>302.2356907571215</v>
+        <v>306.2654999672164</v>
       </c>
       <c r="G77">
         <v>41.4</v>
@@ -7595,28 +7595,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M77">
-        <v>19.37330777753149</v>
+        <v>19.63161854789858</v>
       </c>
       <c r="N77">
-        <v>44.88002555580184</v>
+        <v>44.62171478543475</v>
       </c>
       <c r="O77">
-        <v>11.22000638895046</v>
+        <v>11.15542869635869</v>
       </c>
       <c r="P77">
-        <v>33.66001916685138</v>
+        <v>33.46628608907606</v>
       </c>
       <c r="Q77">
-        <v>67.06001916685139</v>
+        <v>66.86628608907606</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1891034960665695</v>
+        <v>0.1946151689922068</v>
       </c>
       <c r="T77">
-        <v>2.793251868994402</v>
+        <v>2.900684633186494</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.316590748011147</v>
+        <v>3.272951396063632</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08324464055812963</v>
+        <v>0.08315715709961689</v>
       </c>
       <c r="C78">
-        <v>87.23317370970568</v>
+        <v>83.43265843982624</v>
       </c>
       <c r="D78">
-        <v>352.0986736769221</v>
+        <v>352.3279676171377</v>
       </c>
       <c r="E78">
-        <v>-70.01542104227889</v>
+        <v>-65.98561183218391</v>
       </c>
       <c r="F78">
-        <v>306.2654999672164</v>
+        <v>310.2953091773114</v>
       </c>
       <c r="G78">
         <v>41.4</v>
@@ -7677,28 +7677,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M78">
-        <v>19.63161854789858</v>
+        <v>19.88992931826566</v>
       </c>
       <c r="N78">
-        <v>44.62171478543475</v>
+        <v>44.36340401506767</v>
       </c>
       <c r="O78">
-        <v>11.15542869635869</v>
+        <v>11.09085100376692</v>
       </c>
       <c r="P78">
-        <v>33.46628608907606</v>
+        <v>33.27255301130075</v>
       </c>
       <c r="Q78">
-        <v>66.86628608907606</v>
+        <v>66.67255301130075</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1946151689922068</v>
+        <v>0.2006061178244213</v>
       </c>
       <c r="T78">
-        <v>2.900684633186494</v>
+        <v>3.017459376873552</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.272951396063632</v>
+        <v>3.230445533777091</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08315715709961689</v>
+        <v>0.08306967364110414</v>
       </c>
       <c r="C79">
-        <v>83.43265843982624</v>
+        <v>79.63244200647006</v>
       </c>
       <c r="D79">
-        <v>352.3279676171377</v>
+        <v>352.5575603938764</v>
       </c>
       <c r="E79">
-        <v>-65.98561183218391</v>
+        <v>-61.95580262208898</v>
       </c>
       <c r="F79">
-        <v>310.2953091773114</v>
+        <v>314.3251183874063</v>
       </c>
       <c r="G79">
         <v>41.4</v>
@@ -7759,28 +7759,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M79">
-        <v>19.88992931826566</v>
+        <v>20.14824008863275</v>
       </c>
       <c r="N79">
-        <v>44.36340401506767</v>
+        <v>44.10509324470058</v>
       </c>
       <c r="O79">
-        <v>11.09085100376692</v>
+        <v>11.02627331117515</v>
       </c>
       <c r="P79">
-        <v>33.27255301130075</v>
+        <v>33.07881993352544</v>
       </c>
       <c r="Q79">
-        <v>66.67255301130075</v>
+        <v>66.47881993352544</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2006061178244213</v>
+        <v>0.2071416983686552</v>
       </c>
       <c r="T79">
-        <v>3.017459376873552</v>
+        <v>3.144850006350341</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.230445533777091</v>
+        <v>3.189029565395334</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08306967364110414</v>
+        <v>0.0829821901825914</v>
       </c>
       <c r="C80">
-        <v>79.63244200647006</v>
+        <v>75.83252499422383</v>
       </c>
       <c r="D80">
-        <v>352.5575603938764</v>
+        <v>352.7874525917252</v>
       </c>
       <c r="E80">
-        <v>-61.95580262208898</v>
+        <v>-57.925993411994</v>
       </c>
       <c r="F80">
-        <v>314.3251183874063</v>
+        <v>318.3549275975013</v>
       </c>
       <c r="G80">
         <v>41.4</v>
@@ -7841,28 +7841,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M80">
-        <v>20.14824008863275</v>
+        <v>20.40655085899984</v>
       </c>
       <c r="N80">
-        <v>44.10509324470058</v>
+        <v>43.84678247433349</v>
       </c>
       <c r="O80">
-        <v>11.02627331117515</v>
+        <v>10.96169561858337</v>
       </c>
       <c r="P80">
-        <v>33.07881993352544</v>
+        <v>32.88508685575012</v>
       </c>
       <c r="Q80">
-        <v>66.47881993352544</v>
+        <v>66.28508685575011</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2071416983686552</v>
+        <v>0.2142997151551972</v>
       </c>
       <c r="T80">
-        <v>3.144850006350341</v>
+        <v>3.284373076729682</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.189029565395334</v>
+        <v>3.148662102542228</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0829821901825914</v>
+        <v>0.08289470672407866</v>
       </c>
       <c r="C81">
-        <v>75.83252499422383</v>
+        <v>72.03290798920051</v>
       </c>
       <c r="D81">
-        <v>352.7874525917252</v>
+        <v>353.0176447967968</v>
       </c>
       <c r="E81">
-        <v>-57.925993411994</v>
+        <v>-53.89618420189908</v>
       </c>
       <c r="F81">
-        <v>318.3549275975013</v>
+        <v>322.3847368075963</v>
       </c>
       <c r="G81">
         <v>41.4</v>
@@ -7923,28 +7923,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M81">
-        <v>20.40655085899984</v>
+        <v>20.66486162936692</v>
       </c>
       <c r="N81">
-        <v>43.84678247433349</v>
+        <v>43.58847170396641</v>
       </c>
       <c r="O81">
-        <v>10.96169561858337</v>
+        <v>10.8971179259916</v>
       </c>
       <c r="P81">
-        <v>32.88508685575012</v>
+        <v>32.6913537779748</v>
       </c>
       <c r="Q81">
-        <v>66.28508685575011</v>
+        <v>66.0913537779748</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2142997151551972</v>
+        <v>0.2221735336203933</v>
       </c>
       <c r="T81">
-        <v>3.284373076729682</v>
+        <v>3.437848454146957</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.148662102542228</v>
+        <v>3.10930382626045</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08289470672407866</v>
+        <v>0.08280722326556592</v>
       </c>
       <c r="C82">
-        <v>72.03290798920051</v>
+        <v>68.23359157904343</v>
       </c>
       <c r="D82">
-        <v>353.0176447967968</v>
+        <v>353.2481375967347</v>
       </c>
       <c r="E82">
-        <v>-53.89618420189908</v>
+        <v>-49.86637499180409</v>
       </c>
       <c r="F82">
-        <v>322.3847368075963</v>
+        <v>326.4145460176912</v>
       </c>
       <c r="G82">
         <v>41.4</v>
@@ -8005,28 +8005,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M82">
-        <v>20.66486162936692</v>
+        <v>20.92317239973401</v>
       </c>
       <c r="N82">
-        <v>43.58847170396641</v>
+        <v>43.33016093359932</v>
       </c>
       <c r="O82">
-        <v>10.8971179259916</v>
+        <v>10.83254023339983</v>
       </c>
       <c r="P82">
-        <v>32.6913537779748</v>
+        <v>32.49762070019949</v>
       </c>
       <c r="Q82">
-        <v>66.0913537779748</v>
+        <v>65.8976207001995</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2221735336203933</v>
+        <v>0.2308761750819259</v>
       </c>
       <c r="T82">
-        <v>3.437848454146957</v>
+        <v>3.607479134450261</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.10930382626045</v>
+        <v>3.07091735926958</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08280722326556592</v>
+        <v>0.08271973980705316</v>
       </c>
       <c r="C83">
-        <v>68.23359157904343</v>
+        <v>64.43457635293197</v>
       </c>
       <c r="D83">
-        <v>353.2481375967347</v>
+        <v>353.4789315807182</v>
       </c>
       <c r="E83">
-        <v>-49.86637499180409</v>
+        <v>-45.83656578170917</v>
       </c>
       <c r="F83">
-        <v>326.4145460176912</v>
+        <v>330.4443552277862</v>
       </c>
       <c r="G83">
         <v>41.4</v>
@@ -8087,28 +8087,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M83">
-        <v>20.92317239973401</v>
+        <v>21.1814831701011</v>
       </c>
       <c r="N83">
-        <v>43.33016093359932</v>
+        <v>43.07185016323223</v>
       </c>
       <c r="O83">
-        <v>10.83254023339983</v>
+        <v>10.76796254080806</v>
       </c>
       <c r="P83">
-        <v>32.49762070019949</v>
+        <v>32.30388762242418</v>
       </c>
       <c r="Q83">
-        <v>65.8976207001995</v>
+        <v>65.70388762242418</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2308761750819259</v>
+        <v>0.2405457767058509</v>
       </c>
       <c r="T83">
-        <v>3.607479134450261</v>
+        <v>3.795957668120598</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.07091735926958</v>
+        <v>3.033467147571171</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08271973980705316</v>
+        <v>0.0874877563485404</v>
       </c>
       <c r="C84">
-        <v>64.43457635293197</v>
+        <v>48.25062681916262</v>
       </c>
       <c r="D84">
-        <v>353.4789315807182</v>
+        <v>341.3247912570438</v>
       </c>
       <c r="E84">
-        <v>-45.83656578170917</v>
+        <v>-41.80675657161419</v>
       </c>
       <c r="F84">
-        <v>330.4443552277862</v>
+        <v>334.4741644378811</v>
       </c>
       <c r="G84">
         <v>41.4</v>
@@ -8169,45 +8169,45 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M84">
-        <v>21.1814831701011</v>
+        <v>24.04869242308365</v>
       </c>
       <c r="N84">
-        <v>43.07185016323223</v>
+        <v>40.20464091024968</v>
       </c>
       <c r="O84">
-        <v>10.76796254080806</v>
+        <v>10.05116022756242</v>
       </c>
       <c r="P84">
-        <v>32.30388762242418</v>
+        <v>30.15348068268726</v>
       </c>
       <c r="Q84">
-        <v>65.70388762242418</v>
+        <v>63.55348068268726</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2405457767058509</v>
+        <v>0.251352978520826</v>
       </c>
       <c r="T84">
-        <v>3.795957668120598</v>
+        <v>4.006610146928623</v>
       </c>
       <c r="U84">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V84">
         <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>3.033467147571171</v>
+        <v>2.671801535107929</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0874877563485404</v>
+        <v>0.08745877289002767</v>
       </c>
       <c r="C85">
-        <v>48.25062681916262</v>
+        <v>44.29217382028548</v>
       </c>
       <c r="D85">
-        <v>341.3247912570438</v>
+        <v>341.3961474682616</v>
       </c>
       <c r="E85">
-        <v>-41.80675657161419</v>
+        <v>-37.77694736151921</v>
       </c>
       <c r="F85">
-        <v>334.4741644378811</v>
+        <v>338.5039736479761</v>
       </c>
       <c r="G85">
         <v>41.4</v>
@@ -8251,28 +8251,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M85">
-        <v>24.04869242308365</v>
+        <v>24.33843570528948</v>
       </c>
       <c r="N85">
-        <v>40.20464091024968</v>
+        <v>39.91489762804385</v>
       </c>
       <c r="O85">
-        <v>10.05116022756242</v>
+        <v>9.978724407010962</v>
       </c>
       <c r="P85">
-        <v>30.15348068268726</v>
+        <v>29.93617322103288</v>
       </c>
       <c r="Q85">
-        <v>63.55348068268726</v>
+        <v>63.33617322103288</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.251352978520826</v>
+        <v>0.263511080562673</v>
       </c>
       <c r="T85">
-        <v>4.006610146928623</v>
+        <v>4.243594185587652</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.671801535107929</v>
+        <v>2.639994373975691</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08745877289002765</v>
+        <v>0.08742978943151491</v>
       </c>
       <c r="C86">
-        <v>44.29217382028554</v>
+        <v>40.33375066262533</v>
       </c>
       <c r="D86">
-        <v>341.3961474682616</v>
+        <v>341.4675335206963</v>
       </c>
       <c r="E86">
-        <v>-37.77694736151926</v>
+        <v>-33.74713815142434</v>
       </c>
       <c r="F86">
-        <v>338.5039736479761</v>
+        <v>342.533782858071</v>
       </c>
       <c r="G86">
         <v>41.4</v>
@@ -8333,28 +8333,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M86">
-        <v>24.33843570528948</v>
+        <v>24.62817898749531</v>
       </c>
       <c r="N86">
-        <v>39.91489762804385</v>
+        <v>39.62515434583803</v>
       </c>
       <c r="O86">
-        <v>9.978724407010962</v>
+        <v>9.906288586459507</v>
       </c>
       <c r="P86">
-        <v>29.93617322103288</v>
+        <v>29.71886575937852</v>
       </c>
       <c r="Q86">
-        <v>63.33617322103288</v>
+        <v>63.11886575937852</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2635110805626729</v>
+        <v>0.2772902628767661</v>
       </c>
       <c r="T86">
-        <v>4.243594185587648</v>
+        <v>4.51217609606788</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.639994373975692</v>
+        <v>2.608935616634802</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08742978943151491</v>
+        <v>0.08740080597300218</v>
       </c>
       <c r="C87">
-        <v>40.33375066262533</v>
+        <v>36.37535736490526</v>
       </c>
       <c r="D87">
-        <v>341.4675335206963</v>
+        <v>341.5389494330713</v>
       </c>
       <c r="E87">
-        <v>-33.74713815142434</v>
+        <v>-29.71732894132936</v>
       </c>
       <c r="F87">
-        <v>342.533782858071</v>
+        <v>346.563592068166</v>
       </c>
       <c r="G87">
         <v>41.4</v>
@@ -8415,28 +8415,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M87">
-        <v>24.62817898749531</v>
+        <v>24.91792226970114</v>
       </c>
       <c r="N87">
-        <v>39.62515434583803</v>
+        <v>39.33541106363219</v>
       </c>
       <c r="O87">
-        <v>9.906288586459507</v>
+        <v>9.833852765908048</v>
       </c>
       <c r="P87">
-        <v>29.71886575937852</v>
+        <v>29.50155829772415</v>
       </c>
       <c r="Q87">
-        <v>63.11886575937852</v>
+        <v>62.90155829772414</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2772902628767661</v>
+        <v>0.2930378998071583</v>
       </c>
       <c r="T87">
-        <v>4.51217609606788</v>
+        <v>4.819126850902429</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.608935616634802</v>
+        <v>2.578599155976257</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08740080597300218</v>
+        <v>0.08737182251448943</v>
       </c>
       <c r="C88">
-        <v>36.37535736490526</v>
+        <v>32.41699394586442</v>
       </c>
       <c r="D88">
-        <v>341.5389494330713</v>
+        <v>341.6103952241253</v>
       </c>
       <c r="E88">
-        <v>-29.71732894132936</v>
+        <v>-25.68751973123443</v>
       </c>
       <c r="F88">
-        <v>346.563592068166</v>
+        <v>350.5934012782609</v>
       </c>
       <c r="G88">
         <v>41.4</v>
@@ -8497,28 +8497,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M88">
-        <v>24.91792226970114</v>
+        <v>25.20766555190696</v>
       </c>
       <c r="N88">
-        <v>39.33541106363219</v>
+        <v>39.04566778142637</v>
       </c>
       <c r="O88">
-        <v>9.833852765908048</v>
+        <v>9.761416945356594</v>
       </c>
       <c r="P88">
-        <v>29.50155829772415</v>
+        <v>29.28425083606978</v>
       </c>
       <c r="Q88">
-        <v>62.90155829772414</v>
+        <v>62.68425083606978</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2930378998071583</v>
+        <v>0.3112082501114571</v>
       </c>
       <c r="T88">
-        <v>4.819126850902429</v>
+        <v>5.173300798788448</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.578599155976257</v>
+        <v>2.54896008521791</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08737182251448943</v>
+        <v>0.08734283905597667</v>
       </c>
       <c r="C89">
-        <v>32.41699394586442</v>
+        <v>28.45866042425746</v>
       </c>
       <c r="D89">
-        <v>341.6103952241253</v>
+        <v>341.6818709126134</v>
       </c>
       <c r="E89">
-        <v>-25.68751973123443</v>
+        <v>-21.65771052113945</v>
       </c>
       <c r="F89">
-        <v>350.5934012782609</v>
+        <v>354.6232104883559</v>
       </c>
       <c r="G89">
         <v>41.4</v>
@@ -8579,28 +8579,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M89">
-        <v>25.20766555190696</v>
+        <v>25.49740883411279</v>
       </c>
       <c r="N89">
-        <v>39.04566778142637</v>
+        <v>38.75592449922054</v>
       </c>
       <c r="O89">
-        <v>9.761416945356594</v>
+        <v>9.688981124805135</v>
       </c>
       <c r="P89">
-        <v>29.28425083606978</v>
+        <v>29.06694337441541</v>
       </c>
       <c r="Q89">
-        <v>62.68425083606978</v>
+        <v>62.46694337441541</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3112082501114571</v>
+        <v>0.332406992133139</v>
       </c>
       <c r="T89">
-        <v>5.173300798788448</v>
+        <v>5.586503737988804</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.54896008521791</v>
+        <v>2.51999462970407</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08734283905597667</v>
+        <v>0.08991710559746394</v>
       </c>
       <c r="C90">
-        <v>28.45866042425746</v>
+        <v>18.19500882035862</v>
       </c>
       <c r="D90">
-        <v>341.6818709126134</v>
+        <v>335.4480285188095</v>
       </c>
       <c r="E90">
-        <v>-21.65771052113945</v>
+        <v>-17.62790131104447</v>
       </c>
       <c r="F90">
-        <v>354.6232104883559</v>
+        <v>358.6530196984509</v>
       </c>
       <c r="G90">
         <v>41.4</v>
@@ -8661,45 +8661,45 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M90">
-        <v>25.49740883411279</v>
+        <v>27.18589889314258</v>
       </c>
       <c r="N90">
-        <v>38.75592449922054</v>
+        <v>37.06743444019075</v>
       </c>
       <c r="O90">
-        <v>9.688981124805135</v>
+        <v>9.266858610047688</v>
       </c>
       <c r="P90">
-        <v>29.06694337441541</v>
+        <v>27.80057583014306</v>
       </c>
       <c r="Q90">
-        <v>62.46694337441541</v>
+        <v>61.20057583014307</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.332406992133139</v>
+        <v>0.3574600508860358</v>
       </c>
       <c r="T90">
-        <v>5.586503737988804</v>
+        <v>6.074834484316496</v>
       </c>
       <c r="U90">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V90">
         <v>0.25</v>
       </c>
       <c r="W90">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.51999462970407</v>
+        <v>2.363480184557764</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08991710559746394</v>
+        <v>0.08991737213895119</v>
       </c>
       <c r="C91">
-        <v>18.19500882035862</v>
+        <v>14.16456593083365</v>
       </c>
       <c r="D91">
-        <v>335.4480285188095</v>
+        <v>335.4473948393795</v>
       </c>
       <c r="E91">
-        <v>-17.62790131104447</v>
+        <v>-13.59809210094954</v>
       </c>
       <c r="F91">
-        <v>358.6530196984509</v>
+        <v>362.6828289085458</v>
       </c>
       <c r="G91">
         <v>41.4</v>
@@ -8743,28 +8743,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M91">
-        <v>27.18589889314258</v>
+        <v>27.49135843126777</v>
       </c>
       <c r="N91">
-        <v>37.06743444019075</v>
+        <v>36.76197490206556</v>
       </c>
       <c r="O91">
-        <v>9.266858610047688</v>
+        <v>9.19049372551639</v>
       </c>
       <c r="P91">
-        <v>27.80057583014306</v>
+        <v>27.57148117654917</v>
       </c>
       <c r="Q91">
-        <v>61.20057583014307</v>
+        <v>60.97148117654917</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3574600508860358</v>
+        <v>0.387523721389512</v>
       </c>
       <c r="T91">
-        <v>6.074834484316496</v>
+        <v>6.660831379909729</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.363480184557764</v>
+        <v>2.337219293618233</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08991737213895119</v>
+        <v>0.08991763868043845</v>
       </c>
       <c r="C92">
-        <v>14.16456593083365</v>
+        <v>10.13412304370274</v>
       </c>
       <c r="D92">
-        <v>335.4473948393795</v>
+        <v>335.4467611623435</v>
       </c>
       <c r="E92">
-        <v>-13.59809210094954</v>
+        <v>-9.568282890854562</v>
       </c>
       <c r="F92">
-        <v>362.6828289085458</v>
+        <v>366.7126381186408</v>
       </c>
       <c r="G92">
         <v>41.4</v>
@@ -8825,28 +8825,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M92">
-        <v>27.49135843126777</v>
+        <v>27.79681796939297</v>
       </c>
       <c r="N92">
-        <v>36.76197490206556</v>
+        <v>36.45651536394035</v>
       </c>
       <c r="O92">
-        <v>9.19049372551639</v>
+        <v>9.114128840985089</v>
       </c>
       <c r="P92">
-        <v>27.57148117654917</v>
+        <v>27.34238652295527</v>
       </c>
       <c r="Q92">
-        <v>60.97148117654917</v>
+        <v>60.74238652295526</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.387523721389512</v>
+        <v>0.4242682075604273</v>
       </c>
       <c r="T92">
-        <v>6.660831379909729</v>
+        <v>7.377049807857013</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.337219293618233</v>
+        <v>2.311535565116934</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08991763868043845</v>
+        <v>0.08991790522192571</v>
       </c>
       <c r="C93">
-        <v>10.13412304370274</v>
+        <v>6.103680158966029</v>
       </c>
       <c r="D93">
-        <v>335.4467611623435</v>
+        <v>335.4461274877017</v>
       </c>
       <c r="E93">
-        <v>-9.568282890854562</v>
+        <v>-5.538473680759637</v>
       </c>
       <c r="F93">
-        <v>366.7126381186408</v>
+        <v>370.7424473287357</v>
       </c>
       <c r="G93">
         <v>41.4</v>
@@ -8907,28 +8907,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M93">
-        <v>27.79681796939297</v>
+        <v>28.10227750751817</v>
       </c>
       <c r="N93">
-        <v>36.45651536394035</v>
+        <v>36.15105582581516</v>
       </c>
       <c r="O93">
-        <v>9.114128840985089</v>
+        <v>9.037763956453791</v>
       </c>
       <c r="P93">
-        <v>27.34238652295527</v>
+        <v>27.11329186936137</v>
       </c>
       <c r="Q93">
-        <v>60.74238652295526</v>
+        <v>60.51329186936137</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4242682075604273</v>
+        <v>0.4701988152740715</v>
       </c>
       <c r="T93">
-        <v>7.377049807857013</v>
+        <v>8.272322842791118</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.311535565116934</v>
+        <v>2.286410178539576</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08991790522192571</v>
+        <v>0.08991817176341296</v>
       </c>
       <c r="C94">
-        <v>6.103680158966029</v>
+        <v>2.073237276623274</v>
       </c>
       <c r="D94">
-        <v>335.4461274877017</v>
+        <v>335.445493815454</v>
       </c>
       <c r="E94">
-        <v>-5.538473680759637</v>
+        <v>-1.508664470664655</v>
       </c>
       <c r="F94">
-        <v>370.7424473287357</v>
+        <v>374.7722565388307</v>
       </c>
       <c r="G94">
         <v>41.4</v>
@@ -8989,28 +8989,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M94">
-        <v>28.10227750751817</v>
+        <v>28.40773704564337</v>
       </c>
       <c r="N94">
-        <v>36.15105582581516</v>
+        <v>35.84559628768996</v>
       </c>
       <c r="O94">
-        <v>9.037763956453791</v>
+        <v>8.961399071922489</v>
       </c>
       <c r="P94">
-        <v>27.11329186936137</v>
+        <v>26.88419721576747</v>
       </c>
       <c r="Q94">
-        <v>60.51329186936137</v>
+        <v>60.28419721576746</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4701988152740715</v>
+        <v>0.5292524537630425</v>
       </c>
       <c r="T94">
-        <v>8.272322842791118</v>
+        <v>9.423388173420681</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.286410178539576</v>
+        <v>2.261825122856354</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08991817176341296</v>
+        <v>0.08991843830490021</v>
       </c>
       <c r="C95">
-        <v>2.073237276623274</v>
+        <v>-1.957205603325292</v>
       </c>
       <c r="D95">
-        <v>335.445493815454</v>
+        <v>335.4448601456003</v>
       </c>
       <c r="E95">
-        <v>-1.508664470664655</v>
+        <v>2.52114473943027</v>
       </c>
       <c r="F95">
-        <v>374.7722565388307</v>
+        <v>378.8020657489256</v>
       </c>
       <c r="G95">
         <v>41.4</v>
@@ -9071,28 +9071,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M95">
-        <v>28.40773704564337</v>
+        <v>28.71319658376856</v>
       </c>
       <c r="N95">
-        <v>35.84559628768996</v>
+        <v>35.54013674956477</v>
       </c>
       <c r="O95">
-        <v>8.961399071922489</v>
+        <v>8.885034187391192</v>
       </c>
       <c r="P95">
-        <v>26.88419721576747</v>
+        <v>26.65510256217357</v>
       </c>
       <c r="Q95">
-        <v>60.28419721576746</v>
+        <v>60.05510256217357</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5292524537630425</v>
+        <v>0.6079906384150039</v>
       </c>
       <c r="T95">
-        <v>9.423388173420681</v>
+        <v>10.95814194759343</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.261825122856354</v>
+        <v>2.237763153464266</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08991843830490021</v>
+        <v>0.08991870484638748</v>
       </c>
       <c r="C96">
-        <v>-1.957205603325292</v>
+        <v>-5.987648480880011</v>
       </c>
       <c r="D96">
-        <v>335.4448601456003</v>
+        <v>335.4442264781406</v>
       </c>
       <c r="E96">
-        <v>2.52114473943027</v>
+        <v>6.550953949525251</v>
       </c>
       <c r="F96">
-        <v>378.8020657489256</v>
+        <v>382.8318749590206</v>
       </c>
       <c r="G96">
         <v>41.4</v>
@@ -9153,28 +9153,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M96">
-        <v>28.71319658376856</v>
+        <v>29.01865612189376</v>
       </c>
       <c r="N96">
-        <v>35.54013674956477</v>
+        <v>35.23467721143957</v>
       </c>
       <c r="O96">
-        <v>8.885034187391192</v>
+        <v>8.808669302859892</v>
       </c>
       <c r="P96">
-        <v>26.65510256217357</v>
+        <v>26.42600790857968</v>
       </c>
       <c r="Q96">
-        <v>60.05510256217357</v>
+        <v>59.82600790857968</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6079906384150039</v>
+        <v>0.7182240969277501</v>
       </c>
       <c r="T96">
-        <v>10.95814194759343</v>
+        <v>13.10679723143529</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.237763153464266</v>
+        <v>2.214207751848853</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08991870484638748</v>
+        <v>0.08991897138787472</v>
       </c>
       <c r="C97">
-        <v>-5.987648480880011</v>
+        <v>-10.01809135604054</v>
       </c>
       <c r="D97">
-        <v>335.4442264781406</v>
+        <v>335.443592813075</v>
       </c>
       <c r="E97">
-        <v>6.550953949525251</v>
+        <v>10.58076315962023</v>
       </c>
       <c r="F97">
-        <v>382.8318749590206</v>
+        <v>386.8616841691156</v>
       </c>
       <c r="G97">
         <v>41.4</v>
@@ -9235,28 +9235,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M97">
-        <v>29.01865612189376</v>
+        <v>29.32411566001896</v>
       </c>
       <c r="N97">
-        <v>35.23467721143957</v>
+        <v>34.92921767331437</v>
       </c>
       <c r="O97">
-        <v>8.808669302859892</v>
+        <v>8.732304418328592</v>
       </c>
       <c r="P97">
-        <v>26.42600790857968</v>
+        <v>26.19691325498578</v>
       </c>
       <c r="Q97">
-        <v>59.82600790857968</v>
+        <v>59.59691325498578</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7182240969277501</v>
+        <v>0.8835742846968694</v>
       </c>
       <c r="T97">
-        <v>13.10679723143529</v>
+        <v>16.32978015719807</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.214207751848853</v>
+        <v>2.191143087767093</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08991897138787472</v>
+        <v>0.08991923792936199</v>
       </c>
       <c r="C98">
-        <v>-10.01809135604049</v>
+        <v>-14.048534228807</v>
       </c>
       <c r="D98">
-        <v>335.443592813075</v>
+        <v>335.4429591504035</v>
       </c>
       <c r="E98">
-        <v>10.58076315962018</v>
+        <v>14.6105723697151</v>
       </c>
       <c r="F98">
-        <v>386.8616841691155</v>
+        <v>390.8914933792104</v>
       </c>
       <c r="G98">
         <v>41.4</v>
@@ -9317,28 +9317,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M98">
-        <v>29.32411566001896</v>
+        <v>29.62957519814415</v>
       </c>
       <c r="N98">
-        <v>34.92921767331437</v>
+        <v>34.62375813518918</v>
       </c>
       <c r="O98">
-        <v>8.732304418328592</v>
+        <v>8.655939533797294</v>
       </c>
       <c r="P98">
-        <v>26.19691325498578</v>
+        <v>25.96781860139188</v>
       </c>
       <c r="Q98">
-        <v>59.59691325498578</v>
+        <v>59.36781860139188</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8835742846968673</v>
+        <v>1.159157930978731</v>
       </c>
       <c r="T98">
-        <v>16.32978015719803</v>
+        <v>21.70141836680264</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.191143087767093</v>
+        <v>2.168553983769495</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08991923792936199</v>
+        <v>0.08991950447084923</v>
       </c>
       <c r="C99">
-        <v>-14.048534228807</v>
+        <v>-18.07897709917955</v>
       </c>
       <c r="D99">
-        <v>335.4429591504035</v>
+        <v>335.4423254901259</v>
       </c>
       <c r="E99">
-        <v>14.6105723697151</v>
+        <v>18.64038157981008</v>
       </c>
       <c r="F99">
-        <v>390.8914933792104</v>
+        <v>394.9213025893054</v>
       </c>
       <c r="G99">
         <v>41.4</v>
@@ -9399,28 +9399,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M99">
-        <v>29.62957519814415</v>
+        <v>29.93503473626935</v>
       </c>
       <c r="N99">
-        <v>34.62375813518918</v>
+        <v>34.31829859706398</v>
       </c>
       <c r="O99">
-        <v>8.655939533797294</v>
+        <v>8.579574649265995</v>
       </c>
       <c r="P99">
-        <v>25.96781860139188</v>
+        <v>25.73872394779799</v>
       </c>
       <c r="Q99">
-        <v>59.36781860139188</v>
+        <v>59.13872394779798</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.159157930978731</v>
+        <v>1.71032522354246</v>
       </c>
       <c r="T99">
-        <v>21.70141836680264</v>
+        <v>32.44469478601187</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.168553983769495</v>
+        <v>2.146425881894296</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08991950447084923</v>
+        <v>0.08991977101233649</v>
       </c>
       <c r="C100">
-        <v>-18.07897709917955</v>
+        <v>-22.10941996715803</v>
       </c>
       <c r="D100">
-        <v>335.4423254901259</v>
+        <v>335.4416918322423</v>
       </c>
       <c r="E100">
-        <v>18.64038157981008</v>
+        <v>22.67019078990501</v>
       </c>
       <c r="F100">
-        <v>394.9213025893054</v>
+        <v>398.9511117994003</v>
       </c>
       <c r="G100">
         <v>41.4</v>
@@ -9481,28 +9481,28 @@
         <v>64.25333333333333</v>
       </c>
       <c r="M100">
-        <v>29.93503473626935</v>
+        <v>30.24049427439455</v>
       </c>
       <c r="N100">
-        <v>34.31829859706398</v>
+        <v>34.01283905893878</v>
       </c>
       <c r="O100">
-        <v>8.579574649265995</v>
+        <v>8.503209764734695</v>
       </c>
       <c r="P100">
-        <v>25.73872394779799</v>
+        <v>25.50962929420409</v>
       </c>
       <c r="Q100">
-        <v>59.13872394779798</v>
+        <v>58.90962929420408</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.71032522354246</v>
+        <v>3.363827101233645</v>
       </c>
       <c r="T100">
-        <v>32.44469478601187</v>
+        <v>64.67452404363956</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.146425881894296</v>
+        <v>2.124744812380212</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08991977101233649</v>
-      </c>
-      <c r="C101">
-        <v>-22.10941996715803</v>
-      </c>
-      <c r="D101">
-        <v>335.4416918322423</v>
-      </c>
-      <c r="E101">
-        <v>22.67019078990501</v>
-      </c>
-      <c r="F101">
-        <v>398.9511117994003</v>
-      </c>
-      <c r="G101">
-        <v>41.4</v>
-      </c>
-      <c r="H101">
-        <v>26.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>97.65333333333334</v>
-      </c>
-      <c r="K101">
-        <v>33.4</v>
-      </c>
-      <c r="L101">
-        <v>64.25333333333333</v>
-      </c>
-      <c r="M101">
-        <v>30.24049427439455</v>
-      </c>
-      <c r="N101">
-        <v>34.01283905893878</v>
-      </c>
-      <c r="O101">
-        <v>8.503209764734695</v>
-      </c>
-      <c r="P101">
-        <v>25.50962929420409</v>
-      </c>
-      <c r="Q101">
-        <v>58.90962929420408</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.363827101233645</v>
-      </c>
-      <c r="T101">
-        <v>64.67452404363956</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.124744812380212</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
